--- a/data/wer_papers.xlsx
+++ b/data/wer_papers.xlsx
@@ -63,11 +63,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1458,40 +1457,40 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>wer199811</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="2" t="n">
         <v>1998</v>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>WER1998</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>1st Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Maringá, PR, Brazil, 12 Octuber 1998</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Papers</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Erace-Tool-Uma ferramenta baseada em cenários para à engenharia de requisitos.</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">João Caldas Júnior; </t>
@@ -1499,59 +1498,59 @@
           <r>
             <rPr>
               <b val="1"/>
-              <color rgb="00C00000"/>
+              <color rgb="009C5700"/>
             </rPr>
             <t>Paulo C. Masiero</t>
           </r>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>João Caldas Júnior; Paulo Cesar Masiero</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>Paulo C. Masiero → Paulo Cesar Masiero [revisar: subset]</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="n">
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Paulo C. Masiero → Paulo Cesar Masiero [manual]</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>A tool to support requirements trading is presented. The Tool supports the ERACE approach. This approach starts from the systems requirement document and proposes to specify interactions between the system and its agents (scenarios), and then the scenarios are specified in detail. Heuristics to evolve from the requirements model to the analysis are also presented. An example to illustrates the approach is also presented.</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>Engineering Requirements; Scenarios; Use Cases and UML</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr"/>
-      <c r="P12" s="3" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER1998/caldas_junior.pdf</t>
         </is>
       </c>
-      <c r="Q12" s="3" t="inlineStr">
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER1998/wer199811.html</t>
         </is>
       </c>
-      <c r="R12" s="3" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S12" s="3" t="inlineStr"/>
-      <c r="T12" s="3" t="inlineStr"/>
-      <c r="U12" s="3" t="b">
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2926,14 +2925,7 @@
       <c r="H27" s="2" t="inlineStr">
         <is>
           <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="009C5700"/>
-            </rPr>
-            <t>Juan Sánchez Díaz</t>
-          </r>
-          <r>
-            <t xml:space="preserve">; Alberto Aparicio Vila; </t>
+            <t xml:space="preserve">Juan Sánchez Díaz; Alberto Aparicio Vila; </t>
           </r>
           <r>
             <rPr>
@@ -2949,7 +2941,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Juan Sánchez; Alberto Aparicio Vila; Oscar Pastor; Juan Jose Fons</t>
+          <t>Juan Sánchez Díaz; Alberto Aparicio Vila; Oscar Pastor; Juan Jose Fons</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -2959,7 +2951,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Juan Sánchez Díaz → Juan Sánchez [surname_not_last]; Oscar Pastor López → Oscar Pastor [surname_not_last]</t>
+          <t>Oscar Pastor López → Oscar Pastor [surname_not_last]</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
@@ -5068,40 +5060,40 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>wer200112</t>
         </is>
       </c>
-      <c r="B50" s="3" t="n">
+      <c r="B50" s="2" t="n">
         <v>2001</v>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>WER2001</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>4th Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Buenos Aires, Argentina, 22-23 November 2001</t>
         </is>
       </c>
-      <c r="F50" s="3" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Processo e Gerência de Requisitos</t>
         </is>
       </c>
-      <c r="G50" s="3" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>Requirements Processes: An Experience Report</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Julio Cesar Sampaio do Prado Leite; Soeli T. Fiorini; Amador Durán; Beatriz Bernárdez; </t>
@@ -5109,7 +5101,7 @@
           <r>
             <rPr>
               <b val="1"/>
-              <color rgb="00C00000"/>
+              <color rgb="009C5700"/>
             </rPr>
             <t>Juan Sánchez Diaz</t>
           </r>
@@ -5118,53 +5110,53 @@
           </r>
         </is>
       </c>
-      <c r="I50" s="3" t="inlineStr">
-        <is>
-          <t>Julio Cesar Sampaio do Prado Leite; Soeli T. Fiorini; Amador Durán; Beatriz Bernárdez; Juan Sánchez; Emílio Insfrán Pelozo</t>
-        </is>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="K50" s="3" t="inlineStr">
-        <is>
-          <t>Juan Sánchez Diaz → Juan Sánchez [revisar: surname_not_last]</t>
-        </is>
-      </c>
-      <c r="L50" s="3" t="n">
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Julio Cesar Sampaio do Prado Leite; Soeli T. Fiorini; Amador Durán; Beatriz Bernárdez; Juan Sánchez Díaz; Emílio Insfrán Pelozo</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Juan Sánchez Diaz → Juan Sánchez Díaz [manual]</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="M50" s="3" t="inlineStr">
+      <c r="M50" s="2" t="inlineStr">
         <is>
           <t>Abstract. Processes are certainly a key element in software management. Defining and using processes is believed to be an important factor towards quality. Our paper describes a general process language and the experience on its use by two different research teams with two different requirements processes. The process language is the basic representation for a process reuse repository implemented as a web application. The web application was used in order to describe a process for requirements management and a process for interface generation based on requirements information. We present both processes as well as an evaluation of the prototype. Our results are a confirmation of the importance of process reuse and of the possibility of sharing requirements information by publication, on the web, of requirements processes.</t>
         </is>
       </c>
-      <c r="N50" s="3" t="inlineStr">
+      <c r="N50" s="2" t="inlineStr">
         <is>
           <t>requirements engineering; requirements process; process reuse; requirements management; interface</t>
         </is>
       </c>
-      <c r="O50" s="3" t="inlineStr"/>
-      <c r="P50" s="3" t="inlineStr">
+      <c r="O50" s="2" t="inlineStr"/>
+      <c r="P50" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER2001/leite.pdf</t>
         </is>
       </c>
-      <c r="Q50" s="3" t="inlineStr">
+      <c r="Q50" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER2001/wer200112.html</t>
         </is>
       </c>
-      <c r="R50" s="3" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S50" s="3" t="inlineStr"/>
-      <c r="T50" s="3" t="inlineStr"/>
-      <c r="U50" s="3" t="b">
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5254,87 +5246,100 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>wer200114</t>
         </is>
       </c>
-      <c r="B52" t="n">
+      <c r="B52" s="2" t="n">
         <v>2001</v>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>WER2001</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>4th Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Buenos Aires, Argentina, 22-23 November 2001</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Qualidade de Requisitos</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>Automatic Derivation of Workflow Specifications from Organizational Structures and Use Cases</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Maria Carmen Penadés; José H. Canós; Juan Sánchez</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Maria Carmen Penadés; José H. Canós; Juan Sánchez</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="n">
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Maria Carmen Penadés; José H. Canós; </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="009C5700"/>
+            </rPr>
+            <t>Juan Sánchez</t>
+          </r>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Maria Carmen Penadés; José H. Canós; Juan Sánchez Díaz</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Juan Sánchez → Juan Sánchez Díaz [manual]</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="M52" s="2" t="inlineStr">
         <is>
           <t>Workflow technology has reached a reasonable degree of maturity, with a number of both research prototypes and commercial systems available. However, methodological issues have received little attention, and WF developers often have to face the WF development process with neither a methodological support nor a global view of the process. In this paper, we introduce a requirements engineering layer in the workflow development lifecycle. It is organization-based, and follows a bottom-up modeling strategy. In order to capture business processes requirements to obtain a workflow model, we describe the tasks in the process as use cases. The use case model is refined by applying specialization, use and extension relationships, as we go up in the organizational hierarchy. A preliminary workflow model implementing the business processes is obtained automatically from the use case model. The transformation is driven by a set of rules derived from the equivalencies between use case and workflow concepts plus a set of process patterns. A tool supporting our method has been implemented and is outlined in this work.</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="N52" s="2" t="inlineStr">
         <is>
           <t>Workflow specification; use cases; business processes requirements.</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
+      <c r="O52" s="2" t="inlineStr"/>
+      <c r="P52" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER2001/penades.pdf</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="Q52" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER2001/wer200114.html</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="b">
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6379,45 +6384,45 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>wer200206</t>
         </is>
       </c>
-      <c r="B64" s="3" t="n">
+      <c r="B64" s="2" t="n">
         <v>2002</v>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>WER2002</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>5th Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Valencia, Spain, 11-12 November 2002</t>
         </is>
       </c>
-      <c r="F64" s="3" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Papers</t>
         </is>
       </c>
-      <c r="G64" s="3" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>Capturing Web Application Requirements through Goal-Oriented Analysis</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <r>
             <rPr>
               <b val="1"/>
-              <color rgb="00C00000"/>
+              <color rgb="009C5700"/>
             </rPr>
             <t>D. Bolchini</t>
           </r>
@@ -6426,53 +6431,53 @@
           </r>
         </is>
       </c>
-      <c r="I64" s="3" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr">
         <is>
           <t>Davide Bolchini; P. Paolini</t>
         </is>
       </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="K64" s="3" t="inlineStr">
-        <is>
-          <t>D. Bolchini → Davide Bolchini [revisar: initials]</t>
-        </is>
-      </c>
-      <c r="L64" s="3" t="n">
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>D. Bolchini → Davide Bolchini [manual]</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M64" s="3" t="inlineStr">
+      <c r="M64" s="2" t="inlineStr">
         <is>
           <t>New conceptual tools for effectively supporting the activity of requirements analysis of web applications are needed. Current approaches and model in Requirements Engineering (RE) can be tailored and extended in order to cope with the following distinctive features of interactive and hypermediaintensive web applications: a) high-level communication and business goals have to be addressed and carefully analyzed as an integral part of requirements management; b) goals and needs of the stakeholders need to be tied up with design in a coherent fashion, bridging the current gap between requirements and hypermedia specifications; c) lightweight, usable and informal models are needed for web designers and analysts with no engineering background. Starting from key achievements in RE this paper introduces a light-weight methodology blending goal-directed RE and scenario-based techniques. The core elements of the methodology will be illustrated through a real project experience.</t>
         </is>
       </c>
-      <c r="N64" s="3" t="inlineStr"/>
-      <c r="O64" s="3" t="inlineStr"/>
-      <c r="P64" s="3" t="inlineStr">
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr"/>
+      <c r="P64" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER2002/bolchini.pdf</t>
         </is>
       </c>
-      <c r="Q64" s="3" t="inlineStr">
+      <c r="Q64" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER2002/wer200206.html</t>
         </is>
       </c>
-      <c r="R64" s="3" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S64" s="3" t="inlineStr">
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S64" s="2" t="inlineStr">
         <is>
           <t>84-96023-01-X</t>
         </is>
       </c>
-      <c r="T64" s="3" t="inlineStr"/>
-      <c r="U64" s="3" t="b">
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6658,7 +6663,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Hugo Estrada; Alicia Martínez; Oscar Pastor; Juan Sánchez</t>
+          <t>Hugo Estrada; Alicia Martínez; Oscar Pastor; Juan Sánchez Díaz</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -6668,7 +6673,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>H. Estrada → Hugo Estrada [initials]; A. Martinez → Alicia Martínez [initials]; O. Pastor → Oscar Pastor [surname_not_last]; J. Sanchez → Juan Sánchez [surname_not_last]</t>
+          <t>H. Estrada → Hugo Estrada [initials]; A. Martinez → Alicia Martínez [initials]; O. Pastor → Oscar Pastor [surname_not_last]; J. Sanchez → Juan Sánchez Díaz [manual]</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
@@ -6707,45 +6712,45 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>wer200209</t>
         </is>
       </c>
-      <c r="B67" s="3" t="n">
+      <c r="B67" s="2" t="n">
         <v>2002</v>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>WER2002</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>5th Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E67" s="3" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Valencia, Spain, 11-12 November 2002</t>
         </is>
       </c>
-      <c r="F67" s="3" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Papers</t>
         </is>
       </c>
-      <c r="G67" s="3" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>Uma Proposta para Melhorar o Rastreamento de Requisitos</t>
         </is>
       </c>
-      <c r="H67" s="3" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <r>
             <rPr>
               <b val="1"/>
-              <color rgb="00C00000"/>
+              <color rgb="009C5700"/>
             </rPr>
             <t>M. Toranzo</t>
           </r>
@@ -6760,57 +6765,64 @@
             <t>J.F.B. Castro</t>
           </r>
           <r>
-            <t>; E. Mello</t>
-          </r>
-        </is>
-      </c>
-      <c r="I67" s="3" t="inlineStr">
-        <is>
-          <t>Marco A. Toranzo Céspedes; Jaelson Castro; E. Mello</t>
-        </is>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="K67" s="3" t="inlineStr">
-        <is>
-          <t>M. Toranzo → Marco A. Toranzo Céspedes [revisar: surname_not_last]; J.F.B. Castro → Jaelson Castro [initials]</t>
-        </is>
-      </c>
-      <c r="L67" s="3" t="n">
+            <t xml:space="preserve">; </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="009C5700"/>
+            </rPr>
+            <t>E. Mello</t>
+          </r>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Marco Toranzo; Jaelson Castro; Elton Mello</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>M. Toranzo → Marco Toranzo [manual]; J.F.B. Castro → Jaelson Castro [initials]; E. Mello → Elton Mello [manual]</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M67" s="3" t="inlineStr">
+      <c r="M67" s="2" t="inlineStr">
         <is>
           <t>Many contributions concerned with software quality (DoD-2167A, ISO 9000-3 and Capability Maturity Model) mandate that requirements traceability be practiced. However, they do not provide a model of what information should be captures and used as a part of requirements traceability model. This paper provides an framework to improve the requirements traceability.</t>
         </is>
       </c>
-      <c r="N67" s="3" t="inlineStr"/>
-      <c r="O67" s="3" t="inlineStr"/>
-      <c r="P67" s="3" t="inlineStr">
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr"/>
+      <c r="P67" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER2002/toranzo.pdf</t>
         </is>
       </c>
-      <c r="Q67" s="3" t="inlineStr">
+      <c r="Q67" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER2002/wer200209.html</t>
         </is>
       </c>
-      <c r="R67" s="3" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S67" s="3" t="inlineStr">
+      <c r="R67" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S67" s="2" t="inlineStr">
         <is>
           <t>84-96023-01-X</t>
         </is>
       </c>
-      <c r="T67" s="3" t="inlineStr"/>
-      <c r="U67" s="3" t="b">
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6989,202 +7001,216 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="inlineStr">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>wer200212</t>
         </is>
       </c>
-      <c r="B70" s="3" t="n">
+      <c r="B70" s="2" t="n">
         <v>2002</v>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>WER2002</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>5th Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E70" s="3" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Valencia, Spain, 11-12 November 2002</t>
         </is>
       </c>
-      <c r="F70" s="3" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Papers</t>
         </is>
       </c>
-      <c r="G70" s="3" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>Supporting Cooperative Requirements Engineering with an Automated Tool</t>
         </is>
       </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">D.F. Togneri; </t>
-          </r>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <b val="1"/>
-              <color rgb="00C00000"/>
+              <color rgb="009C5700"/>
+            </rPr>
+            <t>D.F. Togneri</t>
+          </r>
+          <r>
+            <t xml:space="preserve">; </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="009C5700"/>
             </rPr>
             <t>R. de A. Falbo</t>
           </r>
           <r>
-            <t>; C. S. de Menezes</t>
-          </r>
-        </is>
-      </c>
-      <c r="I70" s="3" t="inlineStr">
-        <is>
-          <t>D.F. Togneri; Ricardo de Almeida Falbo; C. S. de Menezes</t>
-        </is>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="K70" s="3" t="inlineStr">
-        <is>
-          <t>R. de A. Falbo → Ricardo de Almeida Falbo [revisar: initials]</t>
-        </is>
-      </c>
-      <c r="L70" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M70" s="3" t="inlineStr">
-        <is>
-          <t>Requirements Engineering  one of the macro -activities of Sofware Engineering  is a systematic process of capturing, modeling and documenting requirements through an iteractive and cooperative approach[13]. Its an activity which require s team work. Groups of people formulate requirements, design and implement a system and execute quality assurance activities during the software process[28]. The cooperative work becomes necessary since solutions require different knowledge and professionals become more specialized[3]. Viewing these aspects, its worthwhile to use computational resources to support the cooperative Requirements Engineering activities. The area of Computer-Supported Cooperative Work (CSCW) is interested in how groups of people working on a cooperative basis can be assisted by computational support[28]. This work investigates how solutions from the CSCW area can support Requirements Engineering activities and introduces CRETA  a Cooperative Requirements Engineering support tool, which intends to integrate groupware applications into applications supporting Requirements Engineering. This tool was developed for the Web, using the object-orientation paradigm.</t>
-        </is>
-      </c>
-      <c r="N70" s="3" t="inlineStr">
-        <is>
-          <t>Cooperative Requirements Engineering; Requirements Engineering; Groupware; CSCW (Computer-Supported Cooperative Work); Software Engineering.</t>
-        </is>
-      </c>
-      <c r="O70" s="3" t="inlineStr"/>
-      <c r="P70" s="3" t="inlineStr">
-        <is>
-          <t>https://werpapers.dimap.ufrn.br/papers/WER2002/togneri.pdf</t>
-        </is>
-      </c>
-      <c r="Q70" s="3" t="inlineStr">
-        <is>
-          <t>https://werpapers.dimap.ufrn.br/proceedings/WER2002/wer200212.html</t>
-        </is>
-      </c>
-      <c r="R70" s="3" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S70" s="3" t="inlineStr">
-        <is>
-          <t>84-96023-01-X</t>
-        </is>
-      </c>
-      <c r="T70" s="3" t="inlineStr"/>
-      <c r="U70" s="3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>wer200213</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="n">
-        <v>2002</v>
-      </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t>WER2002</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t>5th Workshop on Requirements Engineering</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="inlineStr">
-        <is>
-          <t>Valencia, Spain, 11-12 November 2002</t>
-        </is>
-      </c>
-      <c r="F71" s="3" t="inlineStr">
-        <is>
-          <t>Papers</t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="inlineStr">
-        <is>
-          <t>Relato de Experiência de Ensino de Engenharia de Requisitos em um Curso de Mestrado em Sistemas de Informação</t>
-        </is>
-      </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
+            <t xml:space="preserve">; </t>
+          </r>
           <r>
             <rPr>
               <b val="1"/>
-              <color rgb="00C00000"/>
+              <color rgb="009C5700"/>
+            </rPr>
+            <t>C. S. de Menezes</t>
+          </r>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Denise Franzotti Togneri; Ricardo de Almeida Falbo; Crediné Silva de Menezes</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>D.F. Togneri → Denise Franzotti Togneri [manual]; R. de A. Falbo → Ricardo de Almeida Falbo [manual]; C. S. de Menezes → Crediné Silva de Menezes [manual]</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>Requirements Engineering  one of the macro -activities of Sofware Engineering  is a systematic process of capturing, modeling and documenting requirements through an iteractive and cooperative approach[13]. Its an activity which require s team work. Groups of people formulate requirements, design and implement a system and execute quality assurance activities during the software process[28]. The cooperative work becomes necessary since solutions require different knowledge and professionals become more specialized[3]. Viewing these aspects, its worthwhile to use computational resources to support the cooperative Requirements Engineering activities. The area of Computer-Supported Cooperative Work (CSCW) is interested in how groups of people working on a cooperative basis can be assisted by computational support[28]. This work investigates how solutions from the CSCW area can support Requirements Engineering activities and introduces CRETA  a Cooperative Requirements Engineering support tool, which intends to integrate groupware applications into applications supporting Requirements Engineering. This tool was developed for the Web, using the object-orientation paradigm.</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>Cooperative Requirements Engineering; Requirements Engineering; Groupware; CSCW (Computer-Supported Cooperative Work); Software Engineering.</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr"/>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>https://werpapers.dimap.ufrn.br/papers/WER2002/togneri.pdf</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>https://werpapers.dimap.ufrn.br/proceedings/WER2002/wer200212.html</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S70" s="2" t="inlineStr">
+        <is>
+          <t>84-96023-01-X</t>
+        </is>
+      </c>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>wer200213</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>2002</v>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>WER2002</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>5th Workshop on Requirements Engineering</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Valencia, Spain, 11-12 November 2002</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Papers</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Relato de Experiência de Ensino de Engenharia de Requisitos em um Curso de Mestrado em Sistemas de Informação</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="009C5700"/>
             </rPr>
             <t>L.E.G. Martins</t>
           </r>
         </is>
       </c>
-      <c r="I71" s="3" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr">
         <is>
           <t>Luiz Eduardo Galvão Martins</t>
         </is>
       </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="K71" s="3" t="inlineStr">
-        <is>
-          <t>L.E.G. Martins → Luiz Eduardo Galvão Martins [revisar: initials]</t>
-        </is>
-      </c>
-      <c r="L71" s="3" t="n">
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>L.E.G. Martins → Luiz Eduardo Galvão Martins [manual]</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M71" s="3" t="inlineStr">
+      <c r="M71" s="2" t="inlineStr">
         <is>
           <t>Este artigo apresenta um relato de experiência de ensino de Engenharia de Requisitos em um curso de Mestrado em Sistemas de Informação. O objetivo deste relato é discutir alguns indicativos sobre a área de Engenharia de Requisitos que emergiram ao longo da disciplina ministrada, tais como: relevância e aplicabilidade da Engenharia de Requisitos nas atividades profissionais exercidas pelos mestrandos, preferências de interesse sobre as atividades da Engenharia de Requisitos, preferências sobre o uso de algumas técnicas de Engenharia de Requisitos, entre outros. Estes indicativos foram obtidos a partir de dados coletados nos seminários e estudos de caso realizados pelos alunos, e de um questionário aplicado aos alunos no final da disciplina.</t>
         </is>
       </c>
-      <c r="N71" s="3" t="inlineStr"/>
-      <c r="O71" s="3" t="inlineStr"/>
-      <c r="P71" s="3" t="inlineStr">
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr"/>
+      <c r="P71" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER2002/martins2.pdf</t>
         </is>
       </c>
-      <c r="Q71" s="3" t="inlineStr">
+      <c r="Q71" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER2002/wer200213.html</t>
         </is>
       </c>
-      <c r="R71" s="3" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S71" s="3" t="inlineStr">
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
         <is>
           <t>84-96023-01-X</t>
         </is>
       </c>
-      <c r="T71" s="3" t="inlineStr"/>
-      <c r="U71" s="3" t="b">
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7432,45 +7458,45 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="inlineStr">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>wer200216</t>
         </is>
       </c>
-      <c r="B74" s="3" t="n">
+      <c r="B74" s="2" t="n">
         <v>2002</v>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>WER2002</t>
         </is>
       </c>
-      <c r="D74" s="3" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>5th Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E74" s="3" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Valencia, Spain, 11-12 November 2002</t>
         </is>
       </c>
-      <c r="F74" s="3" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Papers</t>
         </is>
       </c>
-      <c r="G74" s="3" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>Writing Use Cases Modelled with Situation Theory</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <r>
             <rPr>
               <b val="1"/>
-              <color rgb="00C00000"/>
+              <color rgb="009C5700"/>
             </rPr>
             <t>F.A.C. Pinheiro</t>
           </r>
@@ -7479,53 +7505,53 @@
           </r>
         </is>
       </c>
-      <c r="I74" s="3" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr">
         <is>
           <t>Francisco A. C. Pinheiro; I.D. López</t>
         </is>
       </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="K74" s="3" t="inlineStr">
-        <is>
-          <t>F.A.C. Pinheiro → Francisco A. C. Pinheiro [revisar: initials]</t>
-        </is>
-      </c>
-      <c r="L74" s="3" t="n">
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>F.A.C. Pinheiro → Francisco A. C. Pinheiro [manual]</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M74" s="3" t="inlineStr">
+      <c r="M74" s="2" t="inlineStr">
         <is>
           <t>This article extends a framework intended to simplify the generation of use cases. The framework allows a concrete and systematic way of describing actions by means of a use case pattern and simple natural language sentences. The framework is composed of a pattern for specifying a use case and a set of guidelines for writing the sentences describing it. These guidelines help the specifier to write natural language sentences that may be easy and uniformly understood. The extension presented in this article uses situation theory to formalise the use cases as situations and to translate the simple sentences into situation theoretic concepts. This article refers to PROSIT, a computational implementation of situation theory, to show how use cases can be described in terms of situation theory.</t>
         </is>
       </c>
-      <c r="N74" s="3" t="inlineStr"/>
-      <c r="O74" s="3" t="inlineStr"/>
-      <c r="P74" s="3" t="inlineStr">
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr"/>
+      <c r="P74" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER2002/pinheiro.pdf</t>
         </is>
       </c>
-      <c r="Q74" s="3" t="inlineStr">
+      <c r="Q74" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER2002/wer200216.html</t>
         </is>
       </c>
-      <c r="R74" s="3" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S74" s="3" t="inlineStr">
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S74" s="2" t="inlineStr">
         <is>
           <t>84-96023-01-X</t>
         </is>
       </c>
-      <c r="T74" s="3" t="inlineStr"/>
-      <c r="U74" s="3" t="b">
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7757,45 +7783,45 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>wer200219</t>
         </is>
       </c>
-      <c r="B77" s="3" t="n">
+      <c r="B77" s="2" t="n">
         <v>2002</v>
       </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
         <is>
           <t>WER2002</t>
         </is>
       </c>
-      <c r="D77" s="3" t="inlineStr">
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>5th Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E77" s="3" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Valencia, Spain, 11-12 November 2002</t>
         </is>
       </c>
-      <c r="F77" s="3" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Papers</t>
         </is>
       </c>
-      <c r="G77" s="3" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>VRU: Un Método para Validar Requisitos y Generar Interfaces de Usuario Multiplataforma</t>
         </is>
       </c>
-      <c r="H77" s="3" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <r>
             <rPr>
               <b val="1"/>
-              <color rgb="00C00000"/>
+              <color rgb="009C5700"/>
             </rPr>
             <t>J. Sánchez</t>
           </r>
@@ -7804,91 +7830,91 @@
           </r>
         </is>
       </c>
-      <c r="I77" s="3" t="inlineStr">
-        <is>
-          <t>Juan Sánchez; J. Belenguer; P. Belenguer; D. Pascual</t>
-        </is>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="K77" s="3" t="inlineStr">
-        <is>
-          <t>J. Sánchez → Juan Sánchez [revisar: surname_not_last]</t>
-        </is>
-      </c>
-      <c r="L77" s="3" t="n">
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>Juan Sánchez Díaz; J. Belenguer; P. Belenguer; D. Pascual</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>J. Sánchez → Juan Sánchez Díaz [manual]</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="M77" s="3" t="inlineStr">
+      <c r="M77" s="2" t="inlineStr">
         <is>
           <t>En el artículo se presenta un método de desarrollo de software que permite por una parte validar requisitos de usuario mediante prototipación automática y por otra generar interfaces de usuario. La generación de las interfaces utiliza como lenguaje intermedio el lenguaje de marcado UIML. Una interfaz en UIML puede ser traducida a diversas plataformas, lenguajes y sistemas operativos. El método es consistente con cualquier método de producción de software que utilice una capa de casos de uso y alguna variante de los diagramas de secuencia para mostrar las interacciones internas en el sistema. La ventaja de la propuesta radica en la utilización de una única definición de interfaz de usuario, que luego puede ser traducida y animada en diversos entornos. Las interfaces, con pequeñas modificaciones, pueden formar parte del producto software final.</t>
         </is>
       </c>
-      <c r="N77" s="3" t="inlineStr"/>
-      <c r="O77" s="3" t="inlineStr"/>
-      <c r="P77" s="3" t="inlineStr">
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr"/>
+      <c r="P77" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER2002/sanchez.pdf</t>
         </is>
       </c>
-      <c r="Q77" s="3" t="inlineStr">
+      <c r="Q77" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER2002/wer200219.html</t>
         </is>
       </c>
-      <c r="R77" s="3" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S77" s="3" t="inlineStr">
+      <c r="R77" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S77" s="2" t="inlineStr">
         <is>
           <t>84-96023-01-X</t>
         </is>
       </c>
-      <c r="T77" s="3" t="inlineStr"/>
-      <c r="U77" s="3" t="b">
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>wer200220</t>
         </is>
       </c>
-      <c r="B78" s="3" t="n">
+      <c r="B78" s="2" t="n">
         <v>2002</v>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>WER2002</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>5th Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E78" s="3" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Valencia, Spain, 11-12 November 2002</t>
         </is>
       </c>
-      <c r="F78" s="3" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Papers</t>
         </is>
       </c>
-      <c r="G78" s="3" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>Metamodeling for Requirements Reuse</t>
         </is>
       </c>
-      <c r="H78" s="3" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">O. López; </t>
@@ -7896,7 +7922,7 @@
           <r>
             <rPr>
               <b val="1"/>
-              <color rgb="00C00000"/>
+              <color rgb="009C5700"/>
             </rPr>
             <t>M.A. Laguna</t>
           </r>
@@ -7905,57 +7931,57 @@
           </r>
         </is>
       </c>
-      <c r="I78" s="3" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr">
         <is>
           <t>O. López; Miguel A. Laguna; F.J. Garcia</t>
         </is>
       </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="K78" s="3" t="inlineStr">
-        <is>
-          <t>M.A. Laguna → Miguel A. Laguna [revisar: initials]</t>
-        </is>
-      </c>
-      <c r="L78" s="3" t="n">
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>M.A. Laguna → Miguel A. Laguna [manual]</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M78" s="3" t="inlineStr">
+      <c r="M78" s="2" t="inlineStr">
         <is>
           <t>Correct requirements determination is a critical factor in software development as it takes resources and it is an error prone activity which can bring tragic consequences to the rest of the software life cycle. Having stored reusable requirements elements, both qualified and classified, in a repository might contribute to taking advantage of software development resources and to reducing the error probability in requirements specifications. However, the diversity of notations and formats, as well as the existence of different levels of requirements description make requirements reuse difficult. In this paper we present a metamodel to integrate some different types of semiformal diagrams into a requirements reuse approach. The description of reusable elements constitutes the basis for benefiting from diverse representations of requirements in the development of specifications by reusing requirements.</t>
         </is>
       </c>
-      <c r="N78" s="3" t="inlineStr">
+      <c r="N78" s="2" t="inlineStr">
         <is>
           <t>Requirements engineering; requirements reuse; metamodeling; use case; scenario; workflow.</t>
         </is>
       </c>
-      <c r="O78" s="3" t="inlineStr"/>
-      <c r="P78" s="3" t="inlineStr">
+      <c r="O78" s="2" t="inlineStr"/>
+      <c r="P78" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER2002/lopez.pdf</t>
         </is>
       </c>
-      <c r="Q78" s="3" t="inlineStr">
+      <c r="Q78" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER2002/wer200220.html</t>
         </is>
       </c>
-      <c r="R78" s="3" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S78" s="3" t="inlineStr">
+      <c r="R78" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S78" s="2" t="inlineStr">
         <is>
           <t>84-96023-01-X</t>
         </is>
       </c>
-      <c r="T78" s="3" t="inlineStr"/>
-      <c r="U78" s="3" t="b">
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10775,45 +10801,45 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="3" t="inlineStr">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>wer200409</t>
         </is>
       </c>
-      <c r="B110" s="3" t="n">
+      <c r="B110" s="2" t="n">
         <v>2004</v>
       </c>
-      <c r="C110" s="3" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
         <is>
           <t>WER2004</t>
         </is>
       </c>
-      <c r="D110" s="3" t="inlineStr">
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>7th Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E110" s="3" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Tandil, Argentina, 9-10 December 2004</t>
         </is>
       </c>
-      <c r="F110" s="3" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Requirements Elicitation</t>
         </is>
       </c>
-      <c r="G110" s="3" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>Factores que Influencian el Análisis de Requerimientos para Sistemas de Información Interorganizacionales</t>
         </is>
       </c>
-      <c r="H110" s="3" t="inlineStr">
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <r>
             <rPr>
               <b val="1"/>
-              <color rgb="00C00000"/>
+              <color rgb="009C5700"/>
             </rPr>
             <t>Luciana C. Ballejos</t>
           </r>
@@ -10822,57 +10848,57 @@
           </r>
         </is>
       </c>
-      <c r="I110" s="3" t="inlineStr">
+      <c r="I110" s="2" t="inlineStr">
         <is>
           <t>Luciana Ballejos; Jorge M. Montagna</t>
         </is>
       </c>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="K110" s="3" t="inlineStr">
-        <is>
-          <t>Luciana C. Ballejos → Luciana Ballejos [revisar: subset]</t>
-        </is>
-      </c>
-      <c r="L110" s="3" t="n">
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>Luciana C. Ballejos → Luciana Ballejos [manual]</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M110" s="3" t="inlineStr">
+      <c r="M110" s="2" t="inlineStr">
         <is>
           <t>El trabajo presenta una metodología básica con los pasos a efectuar previamente al desarrollo de Sistemas de Información Interorganizacionales (SIOs). Ellos conforman el soporte para la ejecución de procesos en las Redes Interorganizacionales (RIOs), nuevas estructuras conformadas por varias organizaciones. Uno de los pasos críticos para el éxito de este tipo de proyectos es el Análisis de Requerimientos. Para hacer frente a ello, se analiza la influencia de un conjunto de factores que caracterizan a las RIOs sobre esta etapa particular para los SIOs. Esto es particularmente importante en ambientes donde la cooperación y coordinación entre varias organizaciones son los objetivos principales.</t>
         </is>
       </c>
-      <c r="N110" s="3" t="inlineStr">
+      <c r="N110" s="2" t="inlineStr">
         <is>
           <t>redes interorganizacionales; sistemas de información interorganizacionales; análisis de requerimientos.</t>
         </is>
       </c>
-      <c r="O110" s="3" t="inlineStr"/>
-      <c r="P110" s="3" t="inlineStr">
+      <c r="O110" s="2" t="inlineStr"/>
+      <c r="P110" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER2004/Luciana_Ballejos.pdf</t>
         </is>
       </c>
-      <c r="Q110" s="3" t="inlineStr">
+      <c r="Q110" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER2004/wer200409.html</t>
         </is>
       </c>
-      <c r="R110" s="3" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S110" s="3" t="inlineStr">
+      <c r="R110" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S110" s="2" t="inlineStr">
         <is>
           <t>950-658-147-9</t>
         </is>
       </c>
-      <c r="T110" s="3" t="inlineStr"/>
-      <c r="U110" s="3" t="b">
+      <c r="T110" s="2" t="inlineStr"/>
+      <c r="U110" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -12425,87 +12451,103 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>wer200504</t>
         </is>
       </c>
-      <c r="B127" t="n">
+      <c r="B127" s="2" t="n">
         <v>2005</v>
       </c>
-      <c r="C127" t="inlineStr">
+      <c r="C127" s="2" t="inlineStr">
         <is>
           <t>WER2005</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>8th Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Porto, Portugal, 13-14 June 2005</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Analysis and modeling</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr">
         <is>
           <t>Metamorfosis: Un Marco para el Análisis de Requisitos Funcionales</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Isabel Díaz; Juan Sánchez; Oscar Pastor</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>Isabel Díaz; Juan Sánchez; Oscar Pastor</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="n">
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Isabel Díaz; </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="009C5700"/>
+            </rPr>
+            <t>Juan Sánchez</t>
+          </r>
+          <r>
+            <t>; Oscar Pastor</t>
+          </r>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>Isabel Díaz; Juan Sánchez Díaz; Oscar Pastor</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>Juan Sánchez → Juan Sánchez Díaz [manual]</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M127" t="inlineStr">
+      <c r="M127" s="2" t="inlineStr">
         <is>
           <t>Este artículo describe el Modelo de Realización de Metamorfosis. El propósito principal de este marco es proporcionar la base conceptual necesaria para el establecimiento de vínculos persistentes y controlables entre la especificación de los requisitos funcionales del sistema (expresado como un Modelo de Casos de Uso) y el producto de su análisis (representado a través de un Modelo de Objetos y un Modelo de Interacción). Metamorfosis permite la deducción automática de los modelos del análisis a partir del texto de los casos de uso. Con este objetivo, el Modelo de Casos de Uso ha sido enriquecido para hacer posible la representación de la información sintáctica y semántica de las acciones de los casos de uso. La utilización de roles para facilitar la comprensión de las representaciones y potenciar la genericidad, es otra característica de Metamorfosis.</t>
         </is>
       </c>
-      <c r="N127" t="inlineStr"/>
-      <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr">
+      <c r="N127" s="2" t="inlineStr"/>
+      <c r="O127" s="2" t="inlineStr"/>
+      <c r="P127" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER2005/isabel_diaz.pdf</t>
         </is>
       </c>
-      <c r="Q127" t="inlineStr">
+      <c r="Q127" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER2005/wer200504.html</t>
         </is>
       </c>
-      <c r="R127" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S127" t="inlineStr">
+      <c r="R127" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S127" s="2" t="inlineStr">
         <is>
           <t>972-752-079-0</t>
         </is>
       </c>
-      <c r="T127" t="inlineStr"/>
-      <c r="U127" t="b">
+      <c r="T127" s="2" t="inlineStr"/>
+      <c r="U127" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13198,40 +13240,40 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="3" t="inlineStr">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>wer200513</t>
         </is>
       </c>
-      <c r="B136" s="3" t="n">
+      <c r="B136" s="2" t="n">
         <v>2005</v>
       </c>
-      <c r="C136" s="3" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
         <is>
           <t>WER2005</t>
         </is>
       </c>
-      <c r="D136" s="3" t="inlineStr">
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>8th Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E136" s="3" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Porto, Portugal, 13-14 June 2005</t>
         </is>
       </c>
-      <c r="F136" s="3" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Cognitive approaches and reuse</t>
         </is>
       </c>
-      <c r="G136" s="3" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr">
         <is>
           <t>Uma Abordagem Baseada em Gestão do Conhecimento para Gerência de Requisitos em Desenvolvimento Distribuído de Software</t>
         </is>
       </c>
-      <c r="H136" s="3" t="inlineStr">
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13246,7 +13288,7 @@
           <r>
             <rPr>
               <b val="1"/>
-              <color rgb="00C00000"/>
+              <color rgb="009C5700"/>
             </rPr>
             <t>Leandro Lopes</t>
           </r>
@@ -13255,57 +13297,57 @@
           </r>
         </is>
       </c>
-      <c r="I136" s="3" t="inlineStr">
+      <c r="I136" s="2" t="inlineStr">
         <is>
           <t>Rodrigo Santos de Espindola; Leandro T. Lopes; Rafael Prikladnicki; Jorge Luiz Nicolas Audy</t>
         </is>
       </c>
-      <c r="J136" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="K136" s="3" t="inlineStr">
-        <is>
-          <t>Rodrigo Espindola → Rodrigo Santos de Espindola [subset]; Leandro Lopes → Leandro T. Lopes [revisar: subset]</t>
-        </is>
-      </c>
-      <c r="L136" s="3" t="n">
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>Rodrigo Espindola → Rodrigo Santos de Espindola [subset]; Leandro Lopes → Leandro T. Lopes [manual]</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="M136" s="3" t="inlineStr">
+      <c r="M136" s="2" t="inlineStr">
         <is>
           <t>A distribuição das equipes de desenvolvimento tem provocado diversos desafios ao processo de software. Dentre os desafios, a engenharia de requisitos destaca-se, sofrendo impacto de fatores como distância, diferença de cultura e fuso-horário, bem como dos meios de comunicação disponíveis. Nesse contexto, o gerenciamento das informações relacionadas a requisitos torna-se crítico para garantir que as informações necessárias sobre um determinado domínio ou aplicação estão disponíveis para as equipes de desenvolvimento, bem como que estas informações sejam organizadas de forma a permitir futuro acesso por projetos de manutenção no mesmo escopo. Nesse sentido, este artigo propõe-se a analisar a engenharia de requisitos em projetos de desenvolvimento distribuído de software sob a ótica da gestão de conhecimento. A principal contribuição apresentada é a identificação das informações pertencentes às categorias de conhecimento envolvidas, bem como a forma com que devem ser disponibilizadas.</t>
         </is>
       </c>
-      <c r="N136" s="3" t="inlineStr">
+      <c r="N136" s="2" t="inlineStr">
         <is>
           <t>Engenharia de Requisitos; Manutenção de Software; Gestão de Conhecimento</t>
         </is>
       </c>
-      <c r="O136" s="3" t="inlineStr"/>
-      <c r="P136" s="3" t="inlineStr">
+      <c r="O136" s="2" t="inlineStr"/>
+      <c r="P136" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER2005/rodrigo_espindola.pdf</t>
         </is>
       </c>
-      <c r="Q136" s="3" t="inlineStr">
+      <c r="Q136" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER2005/wer200513.html</t>
         </is>
       </c>
-      <c r="R136" s="3" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S136" s="3" t="inlineStr">
+      <c r="R136" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S136" s="2" t="inlineStr">
         <is>
           <t>972-752-079-0</t>
         </is>
       </c>
-      <c r="T136" s="3" t="inlineStr"/>
-      <c r="U136" s="3" t="b">
+      <c r="T136" s="2" t="inlineStr"/>
+      <c r="U136" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13969,7 +14011,17 @@
       <c r="H144" s="2" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Isabel Villanueva; Juan Sánchez; </t>
+            <t xml:space="preserve">Isabel Villanueva; </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="009C5700"/>
+            </rPr>
+            <t>Juan Sánchez</t>
+          </r>
+          <r>
+            <t xml:space="preserve">; </t>
           </r>
           <r>
             <rPr>
@@ -13982,7 +14034,7 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>Isabel Villanueva; Juan Sánchez; Oscar Pastor</t>
+          <t>Isabel Villanueva; Juan Sánchez Díaz; Oscar Pastor</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
@@ -13992,7 +14044,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>Óscar Pastor → Oscar Pastor [surname_not_last]</t>
+          <t>Juan Sánchez → Juan Sánchez Díaz [manual]; Óscar Pastor → Oscar Pastor [surname_not_last]</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
@@ -14237,7 +14289,17 @@
       <c r="H147" s="2" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Fernanda Alencar; Juan Sánchez; </t>
+            <t xml:space="preserve">Fernanda Alencar; </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="009C5700"/>
+            </rPr>
+            <t>Juan Sánchez</t>
+          </r>
+          <r>
+            <t xml:space="preserve">; </t>
           </r>
           <r>
             <rPr>
@@ -14250,7 +14312,7 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>Fernanda Alencar; Juan Sánchez; Vera Maria Benjamim Werneck</t>
+          <t>Fernanda Alencar; Juan Sánchez Díaz; Vera Maria Benjamim Werneck</t>
         </is>
       </c>
       <c r="J147" s="2" t="inlineStr">
@@ -14260,7 +14322,7 @@
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>Vera Werneck → Vera Maria Benjamim Werneck [manual]</t>
+          <t>Juan Sánchez → Juan Sánchez Díaz [manual]; Vera Werneck → Vera Maria Benjamim Werneck [manual]</t>
         </is>
       </c>
       <c r="L147" s="2" t="n">
@@ -14392,45 +14454,45 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="3" t="inlineStr">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>wer200602</t>
         </is>
       </c>
-      <c r="B149" s="3" t="n">
+      <c r="B149" s="2" t="n">
         <v>2006</v>
       </c>
-      <c r="C149" s="3" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
         <is>
           <t>WER2006</t>
         </is>
       </c>
-      <c r="D149" s="3" t="inlineStr">
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>9th Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E149" s="3" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Rio de Janeiro, Brazil, 13-14 July 2006</t>
         </is>
       </c>
-      <c r="F149" s="3" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Requirements</t>
         </is>
       </c>
-      <c r="G149" s="3" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr">
         <is>
           <t>Aplicabilidade de metricas por pontos de função em sistemas baseados em web</t>
         </is>
       </c>
-      <c r="H149" s="3" t="inlineStr">
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <r>
             <rPr>
               <b val="1"/>
-              <color rgb="00C00000"/>
+              <color rgb="009C5700"/>
             </rPr>
             <t>Ariadne Carvalho</t>
           </r>
@@ -14439,100 +14501,100 @@
           </r>
         </is>
       </c>
-      <c r="I149" s="3" t="inlineStr">
+      <c r="I149" s="2" t="inlineStr">
         <is>
           <t>Ariadne M. B. R. Carvalho; Thelma Chiossi; Marcos Drach</t>
         </is>
       </c>
-      <c r="J149" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="K149" s="3" t="inlineStr">
-        <is>
-          <t>Ariadne Carvalho → Ariadne M. B. R. Carvalho [revisar: subset]</t>
-        </is>
-      </c>
-      <c r="L149" s="3" t="n">
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>Ariadne Carvalho → Ariadne M. B. R. Carvalho [manual]</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M149" s="3" t="inlineStr">
+      <c r="M149" s="2" t="inlineStr">
         <is>
           <t>Este trabalho faz uma análise das características computacionais específicas da plataforma Web, com o intuito de avaliar o grau de adequação e aplicabilidade do método de Análise por Pontos de Função (FPA) a este tipo de ambiente, assim como sua contribuição para a estimativa de esforço. Para tal, são aplicadas duas outras métricas, específicas para Web, a um caso real e o resultado é comparado à aplicação do FPA ao mesmo problema.</t>
         </is>
       </c>
-      <c r="N149" s="3" t="inlineStr">
+      <c r="N149" s="2" t="inlineStr">
         <is>
           <t>pontos de função; métricas; sistemas web</t>
         </is>
       </c>
-      <c r="O149" s="3" t="inlineStr"/>
-      <c r="P149" s="3" t="inlineStr">
+      <c r="O149" s="2" t="inlineStr"/>
+      <c r="P149" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER2006/carvalho.pdf</t>
         </is>
       </c>
-      <c r="Q149" s="3" t="inlineStr">
+      <c r="Q149" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER2006/wer200602.html</t>
         </is>
       </c>
-      <c r="R149" s="3" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S149" s="3" t="inlineStr">
+      <c r="R149" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S149" s="2" t="inlineStr">
         <is>
           <t>1413-9014</t>
         </is>
       </c>
-      <c r="T149" s="3" t="inlineStr"/>
-      <c r="U149" s="3" t="b">
+      <c r="T149" s="2" t="inlineStr"/>
+      <c r="U149" s="2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="3" t="inlineStr">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>wer200603</t>
         </is>
       </c>
-      <c r="B150" s="3" t="n">
+      <c r="B150" s="2" t="n">
         <v>2006</v>
       </c>
-      <c r="C150" s="3" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
         <is>
           <t>WER2006</t>
         </is>
       </c>
-      <c r="D150" s="3" t="inlineStr">
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>9th Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E150" s="3" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Rio de Janeiro, Brazil, 13-14 July 2006</t>
         </is>
       </c>
-      <c r="F150" s="3" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Requirements</t>
         </is>
       </c>
-      <c r="G150" s="3" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr">
         <is>
           <t>Um Estudo sobre a Atividade de Elicitação de Requisitos em Projetos de Software da Área Espacial</t>
         </is>
       </c>
-      <c r="H150" s="3" t="inlineStr">
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <r>
             <rPr>
               <b val="1"/>
-              <color rgb="00C00000"/>
+              <color rgb="009C5700"/>
             </rPr>
             <t>Carlos Lahoz</t>
           </r>
@@ -14541,57 +14603,57 @@
           </r>
         </is>
       </c>
-      <c r="I150" s="3" t="inlineStr">
+      <c r="I150" s="2" t="inlineStr">
         <is>
           <t>Carlos Henrique Netto Lahoz; João Batista Camargo Jr.</t>
         </is>
       </c>
-      <c r="J150" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="K150" s="3" t="inlineStr">
-        <is>
-          <t>[separação/grafia dos autores corrigida]; Carlos Lahoz → Carlos Henrique Netto Lahoz [revisar: subset]</t>
-        </is>
-      </c>
-      <c r="L150" s="3" t="n">
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>[separação/grafia dos autores corrigida]; Carlos Lahoz → Carlos Henrique Netto Lahoz [manual]</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M150" s="3" t="inlineStr">
+      <c r="M150" s="2" t="inlineStr">
         <is>
           <t>Dentro do enfoque de que o software começa a atender cada vez mais um número crescente de funcionalidades de sistemas, é fundamental que a atividade de elicitação de requisitos assuma um papel decisivo no esforço de se alcançar um resultado satisfatório e seguro no projeto de um sistema. No que diz respeito a sistemas aeroespaciais críticos, onde a ambigüidade, a não completeza e a falta de requisitos podem provocar acidentes graves, envolvendo prejuízos econômicos, materiais e humanos, obriga a um tratamento mais cuidadoso sobre este assunto. Este artigo apresenta os resultados preliminares de um estudo sobre quais são os principais problemas que a atividade de elicitação de requisitos enfrenta atualmente em projetos espaciais no Brasil, segundo a visão dos autores. O foco principal do trabalho está na identificação dos requisitos de segurança em projetos de desenvolvimento de software.</t>
         </is>
       </c>
-      <c r="N150" s="3" t="inlineStr">
+      <c r="N150" s="2" t="inlineStr">
         <is>
           <t>elicitação de requisitos; processo de software; sistemas aeroespaciais</t>
         </is>
       </c>
-      <c r="O150" s="3" t="inlineStr"/>
-      <c r="P150" s="3" t="inlineStr">
+      <c r="O150" s="2" t="inlineStr"/>
+      <c r="P150" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER2006/lahoz.pdf</t>
         </is>
       </c>
-      <c r="Q150" s="3" t="inlineStr">
+      <c r="Q150" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER2006/wer200603.html</t>
         </is>
       </c>
-      <c r="R150" s="3" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S150" s="3" t="inlineStr">
+      <c r="R150" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S150" s="2" t="inlineStr">
         <is>
           <t>1413-9014</t>
         </is>
       </c>
-      <c r="T150" s="3" t="inlineStr"/>
-      <c r="U150" s="3" t="b">
+      <c r="T150" s="2" t="inlineStr"/>
+      <c r="U150" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -15617,40 +15679,40 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="3" t="inlineStr">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>wer200615</t>
         </is>
       </c>
-      <c r="B162" s="3" t="n">
+      <c r="B162" s="2" t="n">
         <v>2006</v>
       </c>
-      <c r="C162" s="3" t="inlineStr">
+      <c r="C162" s="2" t="inlineStr">
         <is>
           <t>WER2006</t>
         </is>
       </c>
-      <c r="D162" s="3" t="inlineStr">
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>9th Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E162" s="3" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>Rio de Janeiro, Brazil, 13-14 July 2006</t>
         </is>
       </c>
-      <c r="F162" s="3" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Requirements</t>
         </is>
       </c>
-      <c r="G162" s="3" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr">
         <is>
           <t>Técnicas de Inspeção de Documentos de Requisitos de Software: um Estudo Comparativo</t>
         </is>
       </c>
-      <c r="H162" s="3" t="inlineStr">
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Lilian A. Bertini; </t>
@@ -15658,7 +15720,7 @@
           <r>
             <rPr>
               <b val="1"/>
-              <color rgb="00C00000"/>
+              <color rgb="009C5700"/>
             </rPr>
             <t>Tereza G. Kirner</t>
           </r>
@@ -15667,57 +15729,57 @@
           </r>
         </is>
       </c>
-      <c r="I162" s="3" t="inlineStr">
+      <c r="I162" s="2" t="inlineStr">
         <is>
           <t>Lilian A. Bertini; Tereza Gonçalves Kirner; Maria I. Montebelo; Idemauro A. R. Lara</t>
         </is>
       </c>
-      <c r="J162" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="K162" s="3" t="inlineStr">
-        <is>
-          <t>Tereza G. Kirner → Tereza Gonçalves Kirner [revisar: subset]</t>
-        </is>
-      </c>
-      <c r="L162" s="3" t="n">
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>Tereza G. Kirner → Tereza Gonçalves Kirner [manual]</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="M162" s="3" t="inlineStr">
+      <c r="M162" s="2" t="inlineStr">
         <is>
           <t>This paper presents an empirical study on inspection of Software Requirements Specification (SRS) Documents, aiming at evaluate the efficiency of reading techniques applied to these documents. The techniques of Checklist, Scenario, and Perspective were comparatively evaluated, through the inspection of the SRS of a software application, performed by software engineers. The definition and execution of the empirical study were presented and the results were discussed.</t>
         </is>
       </c>
-      <c r="N162" s="3" t="inlineStr">
+      <c r="N162" s="2" t="inlineStr">
         <is>
           <t>SRS; inspeção</t>
         </is>
       </c>
-      <c r="O162" s="3" t="inlineStr"/>
-      <c r="P162" s="3" t="inlineStr">
+      <c r="O162" s="2" t="inlineStr"/>
+      <c r="P162" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER2006/bertini.pdf</t>
         </is>
       </c>
-      <c r="Q162" s="3" t="inlineStr">
+      <c r="Q162" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER2006/wer200615.html</t>
         </is>
       </c>
-      <c r="R162" s="3" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S162" s="3" t="inlineStr">
+      <c r="R162" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S162" s="2" t="inlineStr">
         <is>
           <t>1413-9014</t>
         </is>
       </c>
-      <c r="T162" s="3" t="inlineStr"/>
-      <c r="U162" s="3" t="b">
+      <c r="T162" s="2" t="inlineStr"/>
+      <c r="U162" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -16490,473 +16552,460 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="3" t="inlineStr">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>wer200706</t>
         </is>
       </c>
-      <c r="B171" s="3" t="n">
+      <c r="B171" s="2" t="n">
         <v>2007</v>
       </c>
-      <c r="C171" s="3" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
         <is>
           <t>WER2007</t>
         </is>
       </c>
-      <c r="D171" s="3" t="inlineStr">
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>10th Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E171" s="3" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>Toronto, Canada, 17-18 May 2007</t>
         </is>
       </c>
-      <c r="F171" s="3" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>Regular Papers</t>
         </is>
       </c>
-      <c r="G171" s="3" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr">
         <is>
           <t>Towards Variability Design as Decision Boundary Placement</t>
         </is>
       </c>
-      <c r="H171" s="3" t="inlineStr">
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Catalin Bidian; </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00C00000"/>
-            </rPr>
-            <t>Eric S.K. Yu</t>
-          </r>
-        </is>
-      </c>
-      <c r="I171" s="3" t="inlineStr">
-        <is>
-          <t>Catalin Bidian; Eric Yu</t>
-        </is>
-      </c>
-      <c r="J171" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="K171" s="3" t="inlineStr">
-        <is>
-          <t>Eric S.K. Yu → Eric Yu [revisar: subset]</t>
-        </is>
-      </c>
-      <c r="L171" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M171" s="3" t="inlineStr">
-        <is>
-          <t>Complex information systems have numerous design variables that are systematically decided upon during the design process. In high-variability systems, some of these decisions are left open and deferred to later stages. For example, in product line architectures, some decision variables are used to generate families of products with variations in features. In user-adaptive systems, the behavior of the system is determined at runtime, based on user characteristics and preferences. In this paper, we propose to characterize variability in terms of boundaries in design decision graphs which depict the space of alternatives. A design decision about variability, such as what choices should be left to the user and which ones should be fixed at which stage in the design process, is then a question of where to place that decision boundary along some path in the relevant decision graph.</t>
-        </is>
-      </c>
-      <c r="N171" s="3" t="inlineStr">
-        <is>
-          <t>variability design</t>
-        </is>
-      </c>
-      <c r="O171" s="3" t="inlineStr"/>
-      <c r="P171" s="3" t="inlineStr">
-        <is>
-          <t>https://werpapers.dimap.ufrn.br/papers/WER2007/Pwer07-bidian.pdf</t>
-        </is>
-      </c>
-      <c r="Q171" s="3" t="inlineStr">
-        <is>
-          <t>https://werpapers.dimap.ufrn.br/proceedings/WER2007/wer200706.html</t>
-        </is>
-      </c>
-      <c r="R171" s="3" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S171" s="3" t="inlineStr">
-        <is>
-          <t>978-1-55014-483-3</t>
-        </is>
-      </c>
-      <c r="T171" s="3" t="inlineStr"/>
-      <c r="U171" s="3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>wer200707</t>
-        </is>
-      </c>
-      <c r="B172" t="n">
-        <v>2007</v>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>WER2007</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>10th Workshop on Requirements Engineering</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Toronto, Canada, 17-18 May 2007</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>Regular Papers</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>A Requirements Management Framework for Privacy Compliance</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Sepideh Ghanavati; Daniel Amyot; Liam Peyton</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>Sepideh Ghanavati; Daniel Amyot; Liam Peyton</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr"/>
-      <c r="L172" t="n">
-        <v>3</v>
-      </c>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>Compliance with privacy legislation is a primary concern for health care institutions that are building information systems support for their business processes. This paper describes a requirements management framework that enables health information custodians (HIC) to document and track compliance with privacy legislation. A metamodel is defined for our framework to define compliance tracking links between separate User Requirements Notation models of the HIC and privacy legislation. Using examples from a case study at a major teaching hospital, we show how this framework can be used to manage change and ensure compliance when privacy legislation is amended or the business processes evolved.</t>
-        </is>
-      </c>
-      <c r="N172" t="inlineStr">
-        <is>
-          <t>requirements management</t>
-        </is>
-      </c>
-      <c r="O172" t="inlineStr"/>
-      <c r="P172" t="inlineStr">
-        <is>
-          <t>https://werpapers.dimap.ufrn.br/papers/WER2007/Qwer07-ghanavati.pdf</t>
-        </is>
-      </c>
-      <c r="Q172" t="inlineStr">
-        <is>
-          <t>https://werpapers.dimap.ufrn.br/proceedings/WER2007/wer200707.html</t>
-        </is>
-      </c>
-      <c r="R172" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S172" t="inlineStr">
-        <is>
-          <t>978-1-55014-483-3</t>
-        </is>
-      </c>
-      <c r="T172" t="inlineStr"/>
-      <c r="U172" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>wer200708</t>
-        </is>
-      </c>
-      <c r="B173" t="n">
-        <v>2007</v>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>WER2007</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>10th Workshop on Requirements Engineering</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>Toronto, Canada, 17-18 May 2007</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>Regular Papers</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>O Gerenciamento de Requisitos no Ambiente COCAR</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>André Di Thommazo; Marcos Danilo Martins; Sandra Fabbri</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>André Di Thommazo; Marcos Danilo Martins; Sandra Fabbri</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="n">
-        <v>3</v>
-      </c>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>This research group has been working towards building an environment which helps software development, providing support to some activities mainly based on use case model. The  reading technique TUCCA and a template to specify requirements were previously defined in another work of this group and are the basis of this environment. Aim. The aim of this paper  is to give an overview of COCAR environment, emphasizing the requirement management activities supported by it. Method. Based on literature and several proposals of other authors, we  introduced in the environment some functionalities that support requirement management and provide traceability between the requirements and the use case model. Results. The  environment was used in a simple example of a real company and the results motivated the improvement of the environment and the continuity of this research. Conclusions. The  information provided by the requirement functionalities give relevant support to maintain the requirement exchange controls, consistence and the development planning, supporting and  facilitating some activities related to requirement management.</t>
-        </is>
-      </c>
-      <c r="N173" t="inlineStr">
-        <is>
-          <t>gerenciamento de requisitos</t>
-        </is>
-      </c>
-      <c r="O173" t="inlineStr"/>
-      <c r="P173" t="inlineStr">
-        <is>
-          <t>https://werpapers.dimap.ufrn.br/papers/WER2007/Rwer07-thommazo.pdf</t>
-        </is>
-      </c>
-      <c r="Q173" t="inlineStr">
-        <is>
-          <t>https://werpapers.dimap.ufrn.br/proceedings/WER2007/wer200708.html</t>
-        </is>
-      </c>
-      <c r="R173" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>978-1-55014-483-3</t>
-        </is>
-      </c>
-      <c r="T173" t="inlineStr"/>
-      <c r="U173" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>wer200709</t>
-        </is>
-      </c>
-      <c r="B174" t="n">
-        <v>2007</v>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>WER2007</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>10th Workshop on Requirements Engineering</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>Toronto, Canada, 17-18 May 2007</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>Regular Papers</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>A Strategy for Information Source Identification</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Julio Cesar Sampaio do Prado Leite; Edson Andrade de Moraes; Carlos Eduardo Portela Serra de Castro</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>Julio Cesar Sampaio do Prado Leite; Edson Andrade de Moraes; Carlos Eduardo Portela Serra de Castro</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="n">
-        <v>3</v>
-      </c>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>Eliciting requirements is well known to be a difficult task. Several strategies exist that makes it possible to elicit information from different information sources. These strategies vary and  should be selected in accordance with the situation at hand. For instance, selecting a strategy to a situation where there are available COTS solutions is different from a tailored and specialized software application. This article reports on a strategy to be used before the selection of an elicitation strategy. We are concerned in how to select the information sources that should be taken in consideration for the requirements elicitation. We consider this activity of fundamental importance to the elicitation process. Selecting the appropriate sources is fundamental as to deliver quality requirements. The article describes the proposed strategy and exemplifies it with a well known and published case, The London Ambulance Service.</t>
-        </is>
-      </c>
-      <c r="N174" t="inlineStr">
-        <is>
-          <t>information source; elicitation</t>
-        </is>
-      </c>
-      <c r="O174" t="inlineStr"/>
-      <c r="P174" t="inlineStr">
-        <is>
-          <t>https://werpapers.dimap.ufrn.br/papers/WER2007/Ewer07-leite02.pdf</t>
-        </is>
-      </c>
-      <c r="Q174" t="inlineStr">
-        <is>
-          <t>https://werpapers.dimap.ufrn.br/proceedings/WER2007/wer200709.html</t>
-        </is>
-      </c>
-      <c r="R174" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S174" t="inlineStr">
-        <is>
-          <t>978-1-55014-483-3</t>
-        </is>
-      </c>
-      <c r="T174" t="inlineStr"/>
-      <c r="U174" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
-        <is>
-          <t>wer200710</t>
-        </is>
-      </c>
-      <c r="B175" s="2" t="n">
-        <v>2007</v>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>WER2007</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
-        <is>
-          <t>10th Workshop on Requirements Engineering</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="inlineStr">
-        <is>
-          <t>Toronto, Canada, 17-18 May 2007</t>
-        </is>
-      </c>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>Regular Papers</t>
-        </is>
-      </c>
-      <c r="G175" s="2" t="inlineStr">
-        <is>
-          <t>Descomposición de árboles de metas a partir de modelos de procesos</t>
-        </is>
-      </c>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Jose Luis De la Vara González; David Anes Alcolea; </t>
           </r>
           <r>
             <rPr>
               <b val="1"/>
               <color rgb="009C5700"/>
             </rPr>
-            <t>Juan Sánchez Díaz</t>
-          </r>
-        </is>
-      </c>
-      <c r="I175" s="2" t="inlineStr">
-        <is>
-          <t>Jose Luis De la Vara González; David Anes Alcolea; Juan Sánchez</t>
-        </is>
-      </c>
-      <c r="J175" s="2" t="inlineStr">
+            <t>Eric S.K. Yu</t>
+          </r>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>Catalin Bidian; Eric Yu</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
         <is>
           <t>ajustado</t>
         </is>
       </c>
-      <c r="K175" s="2" t="inlineStr">
-        <is>
-          <t>Juan Sánchez Díaz → Juan Sánchez [surname_not_last]</t>
-        </is>
-      </c>
-      <c r="L175" s="2" t="n">
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>Eric S.K. Yu → Eric Yu [manual]</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>Complex information systems have numerous design variables that are systematically decided upon during the design process. In high-variability systems, some of these decisions are left open and deferred to later stages. For example, in product line architectures, some decision variables are used to generate families of products with variations in features. In user-adaptive systems, the behavior of the system is determined at runtime, based on user characteristics and preferences. In this paper, we propose to characterize variability in terms of boundaries in design decision graphs which depict the space of alternatives. A design decision about variability, such as what choices should be left to the user and which ones should be fixed at which stage in the design process, is then a question of where to place that decision boundary along some path in the relevant decision graph.</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>variability design</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr"/>
+      <c r="P171" s="2" t="inlineStr">
+        <is>
+          <t>https://werpapers.dimap.ufrn.br/papers/WER2007/Pwer07-bidian.pdf</t>
+        </is>
+      </c>
+      <c r="Q171" s="2" t="inlineStr">
+        <is>
+          <t>https://werpapers.dimap.ufrn.br/proceedings/WER2007/wer200706.html</t>
+        </is>
+      </c>
+      <c r="R171" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S171" s="2" t="inlineStr">
+        <is>
+          <t>978-1-55014-483-3</t>
+        </is>
+      </c>
+      <c r="T171" s="2" t="inlineStr"/>
+      <c r="U171" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>wer200707</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>2007</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>WER2007</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>10th Workshop on Requirements Engineering</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Toronto, Canada, 17-18 May 2007</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Regular Papers</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>A Requirements Management Framework for Privacy Compliance</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Sepideh Ghanavati; Daniel Amyot; Liam Peyton</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Sepideh Ghanavati; Daniel Amyot; Liam Peyton</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="n">
         <v>3</v>
       </c>
-      <c r="M175" s="2" t="inlineStr">
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>Compliance with privacy legislation is a primary concern for health care institutions that are building information systems support for their business processes. This paper describes a requirements management framework that enables health information custodians (HIC) to document and track compliance with privacy legislation. A metamodel is defined for our framework to define compliance tracking links between separate User Requirements Notation models of the HIC and privacy legislation. Using examples from a case study at a major teaching hospital, we show how this framework can be used to manage change and ensure compliance when privacy legislation is amended or the business processes evolved.</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>requirements management</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr"/>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>https://werpapers.dimap.ufrn.br/papers/WER2007/Qwer07-ghanavati.pdf</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>https://werpapers.dimap.ufrn.br/proceedings/WER2007/wer200707.html</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>978-1-55014-483-3</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr"/>
+      <c r="U172" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>wer200708</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>2007</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>WER2007</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>10th Workshop on Requirements Engineering</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Toronto, Canada, 17-18 May 2007</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Regular Papers</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>O Gerenciamento de Requisitos no Ambiente COCAR</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>André Di Thommazo; Marcos Danilo Martins; Sandra Fabbri</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>André Di Thommazo; Marcos Danilo Martins; Sandra Fabbri</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="n">
+        <v>3</v>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>This research group has been working towards building an environment which helps software development, providing support to some activities mainly based on use case model. The  reading technique TUCCA and a template to specify requirements were previously defined in another work of this group and are the basis of this environment. Aim. The aim of this paper  is to give an overview of COCAR environment, emphasizing the requirement management activities supported by it. Method. Based on literature and several proposals of other authors, we  introduced in the environment some functionalities that support requirement management and provide traceability between the requirements and the use case model. Results. The  environment was used in a simple example of a real company and the results motivated the improvement of the environment and the continuity of this research. Conclusions. The  information provided by the requirement functionalities give relevant support to maintain the requirement exchange controls, consistence and the development planning, supporting and  facilitating some activities related to requirement management.</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>gerenciamento de requisitos</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr"/>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>https://werpapers.dimap.ufrn.br/papers/WER2007/Rwer07-thommazo.pdf</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>https://werpapers.dimap.ufrn.br/proceedings/WER2007/wer200708.html</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>978-1-55014-483-3</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr"/>
+      <c r="U173" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>wer200709</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>2007</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>WER2007</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>10th Workshop on Requirements Engineering</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Toronto, Canada, 17-18 May 2007</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Regular Papers</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>A Strategy for Information Source Identification</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Julio Cesar Sampaio do Prado Leite; Edson Andrade de Moraes; Carlos Eduardo Portela Serra de Castro</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Julio Cesar Sampaio do Prado Leite; Edson Andrade de Moraes; Carlos Eduardo Portela Serra de Castro</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="n">
+        <v>3</v>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>Eliciting requirements is well known to be a difficult task. Several strategies exist that makes it possible to elicit information from different information sources. These strategies vary and  should be selected in accordance with the situation at hand. For instance, selecting a strategy to a situation where there are available COTS solutions is different from a tailored and specialized software application. This article reports on a strategy to be used before the selection of an elicitation strategy. We are concerned in how to select the information sources that should be taken in consideration for the requirements elicitation. We consider this activity of fundamental importance to the elicitation process. Selecting the appropriate sources is fundamental as to deliver quality requirements. The article describes the proposed strategy and exemplifies it with a well known and published case, The London Ambulance Service.</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>information source; elicitation</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr"/>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>https://werpapers.dimap.ufrn.br/papers/WER2007/Ewer07-leite02.pdf</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>https://werpapers.dimap.ufrn.br/proceedings/WER2007/wer200709.html</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>978-1-55014-483-3</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr"/>
+      <c r="U174" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>wer200710</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>2007</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>WER2007</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>10th Workshop on Requirements Engineering</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Toronto, Canada, 17-18 May 2007</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Regular Papers</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Descomposición de árboles de metas a partir de modelos de procesos</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Jose Luis De la Vara González; David Anes Alcolea; Juan Sánchez Díaz</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Jose Luis De la Vara González; David Anes Alcolea; Juan Sánchez Díaz</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="n">
+        <v>3</v>
+      </c>
+      <c r="M175" t="inlineStr">
         <is>
           <t>Los Sistemas de Información (SI) utilizados dentro de una organización no son algo separado de la organización empresarial a la que le dan soporte, y por tanto la Ingeniería de Requisitos (IR) debe considerar las necesidades de negocio de una organización. Aunque se reconoce que la IR es el puente natural que conecta el mundo empresarial y el mundo de los SI, la mayor parte de la investigación en IR continúa estando orientada a la solución, evitando considerar los problemas reales del mundo empresarial. Las necesidades de negocio pueden ser descritas mediante el alineamiento de los SI con la estrategia del negocio, los procesos de negocio, las infraestructuras organizacionales y las metas organizacionales. Una de las consecuencias del alineamiento entre negocio y los SI es el mapeado de las metas organizacionales y los procesos a la especificación del sistema En este trabajo se presenta una aproximación que utiliza una especificación en la forma de modelo de metas, construida mediante heurísticas en base a modelos de procesos en la forma de BPMN. A partir del modelo de metas, mediante un proceso de refinamiento y de etiquetado, se obtiene un modelo de requisitos en la forma de casos de uso. La especificación así obtenida permite reflejar de manera más cercana las necesidades del negocio y asegura el alineamiento de las mismas con el futuro SI.</t>
         </is>
       </c>
-      <c r="N175" s="2" t="inlineStr">
+      <c r="N175" t="inlineStr">
         <is>
           <t>modelos de procesos metas</t>
         </is>
       </c>
-      <c r="O175" s="2" t="inlineStr"/>
-      <c r="P175" s="2" t="inlineStr">
+      <c r="O175" t="inlineStr"/>
+      <c r="P175" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER2007/Fwer07-gonzales01.pdf</t>
         </is>
       </c>
-      <c r="Q175" s="2" t="inlineStr">
+      <c r="Q175" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER2007/wer200710.html</t>
         </is>
       </c>
-      <c r="R175" s="2" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S175" s="2" t="inlineStr">
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S175" t="inlineStr">
         <is>
           <t>978-1-55014-483-3</t>
         </is>
       </c>
-      <c r="T175" s="2" t="inlineStr"/>
-      <c r="U175" s="2" t="b">
+      <c r="T175" t="inlineStr"/>
+      <c r="U175" t="b">
         <v>0</v>
       </c>
     </row>
@@ -17182,17 +17231,7 @@
             <t>José Luís De la Vara González</t>
           </r>
           <r>
-            <t xml:space="preserve">; </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="009C5700"/>
-            </rPr>
-            <t>Juan Sánchez Díaz</t>
-          </r>
-          <r>
-            <t xml:space="preserve">;  </t>
+            <t xml:space="preserve">; Juan Sánchez Díaz;  </t>
           </r>
           <r>
             <rPr>
@@ -17205,7 +17244,7 @@
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>Jose Luis De la Vara González; Juan Sánchez; Oscar Pastor</t>
+          <t>Jose Luis De la Vara González; Juan Sánchez Díaz; Oscar Pastor</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
@@ -17215,7 +17254,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>José Luís De la Vara González → Jose Luis De la Vara González [same_key]; Juan Sánchez Díaz → Juan Sánchez [surname_not_last]; Óscar Pastor López → Oscar Pastor [surname_not_last]</t>
+          <t>José Luís De la Vara González → Jose Luis De la Vara González [same_key]; Óscar Pastor López → Oscar Pastor [surname_not_last]</t>
         </is>
       </c>
       <c r="L178" s="2" t="n">
@@ -17716,40 +17755,40 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="3" t="inlineStr">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>wer200719</t>
         </is>
       </c>
-      <c r="B184" s="3" t="n">
+      <c r="B184" s="2" t="n">
         <v>2007</v>
       </c>
-      <c r="C184" s="3" t="inlineStr">
+      <c r="C184" s="2" t="inlineStr">
         <is>
           <t>WER2007</t>
         </is>
       </c>
-      <c r="D184" s="3" t="inlineStr">
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>10th Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E184" s="3" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>Toronto, Canada, 17-18 May 2007</t>
         </is>
       </c>
-      <c r="F184" s="3" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>Short Papers</t>
         </is>
       </c>
-      <c r="G184" s="3" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr">
         <is>
           <t>Exploiting a Goal-Decomposition Technique to Prioritize Non-functional Requirements</t>
         </is>
       </c>
-      <c r="H184" s="3" t="inlineStr">
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17774,63 +17813,63 @@
           <r>
             <rPr>
               <b val="1"/>
-              <color rgb="00C00000"/>
+              <color rgb="009C5700"/>
             </rPr>
             <t>O. Ormandjieva</t>
           </r>
         </is>
       </c>
-      <c r="I184" s="3" t="inlineStr">
+      <c r="I184" s="2" t="inlineStr">
         <is>
           <t>Maya Daneva; M. Kassab; M. L. Ponisio; Roel Wieringa; Olga Ormandjieva</t>
         </is>
       </c>
-      <c r="J184" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="K184" s="3" t="inlineStr">
-        <is>
-          <t>M. Daneva → Maya Daneva [initials]; R. J. Wieringa → Roel Wieringa [initials]; O. Ormandjieva → Olga Ormandjieva [revisar: initials]</t>
-        </is>
-      </c>
-      <c r="L184" s="3" t="n">
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K184" s="2" t="inlineStr">
+        <is>
+          <t>M. Daneva → Maya Daneva [initials]; R. J. Wieringa → Roel Wieringa [initials]; O. Ormandjieva → Olga Ormandjieva [manual]</t>
+        </is>
+      </c>
+      <c r="L184" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="M184" s="3" t="inlineStr">
+      <c r="M184" s="2" t="inlineStr">
         <is>
           <t>Business stakeholders need to have clear and realistic goals if they want to meet commitments in application development. As a consequence, at early stages they prioritize requirements. However, requirements do change. The effect of change forces the stakeholders to balance alternatives and reprioritize requirements accordingly. In this paper we discuss the problem of priorities to non-functional requirements subjected to change. We, then, propose an approach to help smooth the impact of such changes. Our approach favors the translation of nonoperational specifications into operational definitions that can be evaluated once the system is developed. It uses the goal-question-metric method as the major support to decompose non-operational specifications into operational ones. We claim that the effort invested in operationalizing NFRs helps dealing with changing requirements during system development. Based on this transformation and in our experience, we provide guidelines to prioritize volatile non-functional requirements.</t>
         </is>
       </c>
-      <c r="N184" s="3" t="inlineStr">
+      <c r="N184" s="2" t="inlineStr">
         <is>
           <t>Non-functional Requirements</t>
         </is>
       </c>
-      <c r="O184" s="3" t="inlineStr"/>
-      <c r="P184" s="3" t="inlineStr">
+      <c r="O184" s="2" t="inlineStr"/>
+      <c r="P184" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER2007/Uwer07-daneva.pdf</t>
         </is>
       </c>
-      <c r="Q184" s="3" t="inlineStr">
+      <c r="Q184" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER2007/wer200719.html</t>
         </is>
       </c>
-      <c r="R184" s="3" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S184" s="3" t="inlineStr">
+      <c r="R184" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S184" s="2" t="inlineStr">
         <is>
           <t>978-1-55014-483-3</t>
         </is>
       </c>
-      <c r="T184" s="3" t="inlineStr"/>
-      <c r="U184" s="3" t="b">
+      <c r="T184" s="2" t="inlineStr"/>
+      <c r="U184" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -18284,87 +18323,100 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr">
+      <c r="A190" s="2" t="inlineStr">
         <is>
           <t>wer200804</t>
         </is>
       </c>
-      <c r="B190" t="n">
+      <c r="B190" s="2" t="n">
         <v>2008</v>
       </c>
-      <c r="C190" t="inlineStr">
+      <c r="C190" s="2" t="inlineStr">
         <is>
           <t>WER2008</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr">
+      <c r="D190" s="2" t="inlineStr">
         <is>
           <t>11th Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr">
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t>Barcelona, Catalonia, Spain, 12-13 September 2008</t>
         </is>
       </c>
-      <c r="F190" t="inlineStr">
+      <c r="F190" s="2" t="inlineStr">
         <is>
           <t>Requirements Analysis</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr">
+      <c r="G190" s="2" t="inlineStr">
         <is>
           <t>Aplicação de Técnicas de Leitura durante a Análise de Requisitos</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Márcia Seabra Cabral; Fernanda Alencar; Jaelson Castro; Oscar Pastor; Juan Sánchez</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>Márcia Seabra Cabral; Fernanda Alencar; Jaelson Castro; Oscar Pastor; Juan Sánchez</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr"/>
-      <c r="L190" t="n">
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Márcia Seabra Cabral; Fernanda Alencar; Jaelson Castro; Oscar Pastor; </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="009C5700"/>
+            </rPr>
+            <t>Juan Sánchez</t>
+          </r>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>Márcia Seabra Cabral; Fernanda Alencar; Jaelson Castro; Oscar Pastor; Juan Sánchez Díaz</t>
+        </is>
+      </c>
+      <c r="J190" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K190" s="2" t="inlineStr">
+        <is>
+          <t>Juan Sánchez → Juan Sánchez Díaz [manual]</t>
+        </is>
+      </c>
+      <c r="L190" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="M190" t="inlineStr">
+      <c r="M190" s="2" t="inlineStr">
         <is>
           <t>This paper describes the result work of the reading techniques application, Checklist and PBR, in the requirements analysis activity during the inspection process to help the inspectors to detect defects. The objective is to analyze the reading technique effectiveness. It presents the experiment result performed in the AMADeUs-MM requirements. será aceito ou não após a atividade de Validação de Requisitos.</t>
         </is>
       </c>
-      <c r="N190" t="inlineStr"/>
-      <c r="O190" t="inlineStr"/>
-      <c r="P190" t="inlineStr">
+      <c r="N190" s="2" t="inlineStr"/>
+      <c r="O190" s="2" t="inlineStr"/>
+      <c r="P190" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER2008/cabral.pdf</t>
         </is>
       </c>
-      <c r="Q190" t="inlineStr">
+      <c r="Q190" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER2008/wer200804.html</t>
         </is>
       </c>
-      <c r="R190" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S190" t="inlineStr">
+      <c r="R190" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S190" s="2" t="inlineStr">
         <is>
           <t>978-84-7653-144-0</t>
         </is>
       </c>
-      <c r="T190" t="inlineStr"/>
-      <c r="U190" t="b">
+      <c r="T190" s="2" t="inlineStr"/>
+      <c r="U190" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -20936,40 +20988,40 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="3" t="inlineStr">
+      <c r="A220" s="2" t="inlineStr">
         <is>
           <t>wer200914</t>
         </is>
       </c>
-      <c r="B220" s="3" t="n">
+      <c r="B220" s="2" t="n">
         <v>2009</v>
       </c>
-      <c r="C220" s="3" t="inlineStr">
+      <c r="C220" s="2" t="inlineStr">
         <is>
           <t>WER2009</t>
         </is>
       </c>
-      <c r="D220" s="3" t="inlineStr">
+      <c r="D220" s="2" t="inlineStr">
         <is>
           <t>12th Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E220" s="3" t="inlineStr">
+      <c r="E220" s="2" t="inlineStr">
         <is>
           <t>Valparaíso, Chile, 16-17 July 2009</t>
         </is>
       </c>
-      <c r="F220" s="3" t="inlineStr">
+      <c r="F220" s="2" t="inlineStr">
         <is>
           <t>Traceability and Product Lines</t>
         </is>
       </c>
-      <c r="G220" s="3" t="inlineStr">
+      <c r="G220" s="2" t="inlineStr">
         <is>
           <t>Towards a requirements reuse method using Product Line in distributed environments</t>
         </is>
       </c>
-      <c r="H220" s="3" t="inlineStr">
+      <c r="H220" s="2" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Thais Ebling; </t>
@@ -20977,7 +21029,7 @@
           <r>
             <rPr>
               <b val="1"/>
-              <color rgb="00C00000"/>
+              <color rgb="009C5700"/>
             </rPr>
             <t>Jorge Luis Nicolas Audy</t>
           </r>
@@ -20986,138 +21038,154 @@
           </r>
         </is>
       </c>
-      <c r="I220" s="3" t="inlineStr">
+      <c r="I220" s="2" t="inlineStr">
         <is>
           <t>Thais Ebling; Jorge Luis N. Audy; Rafael Prikladnicki</t>
         </is>
       </c>
-      <c r="J220" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="K220" s="3" t="inlineStr">
-        <is>
-          <t>Jorge Luis Nicolas Audy → Jorge Luis N. Audy [revisar: subset]</t>
-        </is>
-      </c>
-      <c r="L220" s="3" t="n">
+      <c r="J220" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K220" s="2" t="inlineStr">
+        <is>
+          <t>Jorge Luis Nicolas Audy → Jorge Luis N. Audy [manual]</t>
+        </is>
+      </c>
+      <c r="L220" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M220" s="3" t="inlineStr">
+      <c r="M220" s="2" t="inlineStr">
         <is>
           <t>Distributed Software Development (DSD) is a recent approach where the teams are geographically distributed. Some characteristics of these environments have significant impact in activities that require constant communication, shared vision and stakeholders cooperation, as we have in Requirements Engineering (RE). The goal of this paper is to present a requirements reuse method that integrates software reuse in the context of Product Lines (PL), to improve the RE in a DSD environment.</t>
         </is>
       </c>
-      <c r="N220" s="3" t="inlineStr"/>
-      <c r="O220" s="3" t="inlineStr"/>
-      <c r="P220" s="3" t="inlineStr">
+      <c r="N220" s="2" t="inlineStr"/>
+      <c r="O220" s="2" t="inlineStr"/>
+      <c r="P220" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER2009/ebling.pdf</t>
         </is>
       </c>
-      <c r="Q220" s="3" t="inlineStr">
+      <c r="Q220" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER2009/wer200914.html</t>
         </is>
       </c>
-      <c r="R220" s="3" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S220" s="3" t="inlineStr">
+      <c r="R220" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S220" s="2" t="inlineStr">
         <is>
           <t>978-956-319-941-3</t>
         </is>
       </c>
-      <c r="T220" s="3" t="inlineStr"/>
-      <c r="U220" s="3" t="b">
+      <c r="T220" s="2" t="inlineStr"/>
+      <c r="U220" s="2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="inlineStr">
+      <c r="A221" s="2" t="inlineStr">
         <is>
           <t>wer201001</t>
         </is>
       </c>
-      <c r="B221" t="n">
+      <c r="B221" s="2" t="n">
         <v>2010</v>
       </c>
-      <c r="C221" t="inlineStr">
+      <c r="C221" s="2" t="inlineStr">
         <is>
           <t>WER2010</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr">
+      <c r="D221" s="2" t="inlineStr">
         <is>
           <t>13th Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr">
+      <c r="E221" s="2" t="inlineStr">
         <is>
           <t>Cuenca, Equador, 12-13 April 2010</t>
         </is>
       </c>
-      <c r="F221" t="inlineStr">
+      <c r="F221" s="2" t="inlineStr">
         <is>
           <t>Business Process Modeling - Product Families</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr">
+      <c r="G221" s="2" t="inlineStr">
         <is>
           <t>A Goal-Oriented Approach for Variability in BPMN</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>Emanuel Santos; Jaelson Castro; Juan Sánchez ;Oscar Pastor</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>Emanuel Santos; Jaelson Castro; Juan Sánchez; Oscar Pastor</t>
-        </is>
-      </c>
-      <c r="J221" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K221" t="inlineStr"/>
-      <c r="L221" t="n">
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Emanuel Santos; Jaelson Castro; </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="009C5700"/>
+            </rPr>
+            <t>Juan Sánchez</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> ;Oscar Pastor</t>
+          </r>
+        </is>
+      </c>
+      <c r="I221" s="2" t="inlineStr">
+        <is>
+          <t>Emanuel Santos; Jaelson Castro; Juan Sánchez Díaz; Oscar Pastor</t>
+        </is>
+      </c>
+      <c r="J221" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K221" s="2" t="inlineStr">
+        <is>
+          <t>Juan Sánchez → Juan Sánchez Díaz [manual]</t>
+        </is>
+      </c>
+      <c r="L221" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="M221" t="inlineStr">
+      <c r="M221" s="2" t="inlineStr">
         <is>
           <t>Good business processes need to be up-to-date and automated to represent the organizational environment. To obtain models that reflect the changes it is necessary continuous checking between model and reality. Thus, business process model need to be modifiable and transformable in software. In order satisfy these needs we propose to apply variability analysis over Business Process Models, represented by Business Process Modeling Notation (BPMN), using a Goal-Oriented approach. In this paper we present a high-level process that links different methods in order to describe a systematic way to update BPMN models. Our proposal tries to achieve it by representing variability in goal trees.</t>
         </is>
       </c>
-      <c r="N221" t="inlineStr"/>
-      <c r="O221" t="inlineStr"/>
-      <c r="P221" t="inlineStr">
+      <c r="N221" s="2" t="inlineStr"/>
+      <c r="O221" s="2" t="inlineStr"/>
+      <c r="P221" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER2010/santos.pdf</t>
         </is>
       </c>
-      <c r="Q221" t="inlineStr">
+      <c r="Q221" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER2010/wer201001.html</t>
         </is>
       </c>
-      <c r="R221" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S221" t="inlineStr">
+      <c r="R221" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S221" s="2" t="inlineStr">
         <is>
           <t>978-9978-325-12-4</t>
         </is>
       </c>
-      <c r="T221" t="inlineStr"/>
-      <c r="U221" t="b">
+      <c r="T221" s="2" t="inlineStr"/>
+      <c r="U221" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -21377,103 +21445,91 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="3" t="inlineStr">
+      <c r="A225" s="2" t="inlineStr">
         <is>
           <t>wer201005</t>
         </is>
       </c>
-      <c r="B225" s="3" t="n">
+      <c r="B225" s="2" t="n">
         <v>2010</v>
       </c>
-      <c r="C225" s="3" t="inlineStr">
+      <c r="C225" s="2" t="inlineStr">
         <is>
           <t>WER2010</t>
         </is>
       </c>
-      <c r="D225" s="3" t="inlineStr">
+      <c r="D225" s="2" t="inlineStr">
         <is>
           <t>13th Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E225" s="3" t="inlineStr">
+      <c r="E225" s="2" t="inlineStr">
         <is>
           <t>Cuenca, Equador, 12-13 April 2010</t>
         </is>
       </c>
-      <c r="F225" s="3" t="inlineStr">
+      <c r="F225" s="2" t="inlineStr">
         <is>
           <t>Requirements Elicitation</t>
         </is>
       </c>
-      <c r="G225" s="3" t="inlineStr">
+      <c r="G225" s="2" t="inlineStr">
         <is>
           <t>From User Requirements to Tasks Descriptions in Real-Time Systems</t>
         </is>
       </c>
-      <c r="H225" s="3" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Leo Ordinez; David Donari; </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00C00000"/>
-            </rPr>
-            <t>Rodrigo Santos</t>
-          </r>
-          <r>
-            <t xml:space="preserve"> ;Javier Orozco</t>
-          </r>
-        </is>
-      </c>
-      <c r="I225" s="3" t="inlineStr">
-        <is>
-          <t>Leo Ordinez; David Donari; Rodrigo Santos; Javier Orozco</t>
-        </is>
-      </c>
-      <c r="J225" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="K225" s="3" t="inlineStr">
-        <is>
-          <t>Rodrigo Santos [revisar: ambiguous]</t>
-        </is>
-      </c>
-      <c r="L225" s="3" t="n">
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t>Leo Ordinez; David Donari; Rodrigo Santos ;Javier Orozco</t>
+        </is>
+      </c>
+      <c r="I225" s="2" t="inlineStr">
+        <is>
+          <t>Leo Ordinez; David Donari; Rodrigo Santos (arg); Javier Orozco</t>
+        </is>
+      </c>
+      <c r="J225" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K225" s="2" t="inlineStr">
+        <is>
+          <t>Rodrigo Santos → Rodrigo Santos (arg) [manual]</t>
+        </is>
+      </c>
+      <c r="L225" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="M225" s="3" t="inlineStr">
+      <c r="M225" s="2" t="inlineStr">
         <is>
           <t>Real-time scheduling theory has made a great progress in the last decades. From small devices to enormous satellites or industrial plants take advantage of this ongoing research. However, to the authors belief, there is still a gap to fully exploit the benefits of the theory. The cornerstone of real-time scheduling theory is the concept of task. Nevertheless, very little is mentioned about how to discover such tasks. Thus, the objective of this paper is to propose a systematic way of describing real-time tasks by jeans of requirements elicitation. The process begins with the gathering of user requirements through Use Case Diagrams. Then, tose use cases are refined to turn them into tasks descriptions. Lastly, tasks descriptions are further refined and brought to a detailed characterization of individual execution flows. This final tasks characterization is made with Activity Diagrams. Finally, a Line-Follower System is used to exemplify the proposed approach.</t>
         </is>
       </c>
-      <c r="N225" s="3" t="inlineStr"/>
-      <c r="O225" s="3" t="inlineStr"/>
-      <c r="P225" s="3" t="inlineStr">
+      <c r="N225" s="2" t="inlineStr"/>
+      <c r="O225" s="2" t="inlineStr"/>
+      <c r="P225" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER2010/ordinez.pdf</t>
         </is>
       </c>
-      <c r="Q225" s="3" t="inlineStr">
+      <c r="Q225" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER2010/wer201005.html</t>
         </is>
       </c>
-      <c r="R225" s="3" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S225" s="3" t="inlineStr">
+      <c r="R225" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S225" s="2" t="inlineStr">
         <is>
           <t>978-9978-325-12-4</t>
         </is>
       </c>
-      <c r="T225" s="3" t="inlineStr"/>
-      <c r="U225" s="3" t="b">
+      <c r="T225" s="2" t="inlineStr"/>
+      <c r="U225" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -24611,40 +24667,40 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="3" t="inlineStr">
+      <c r="A259" s="2" t="inlineStr">
         <is>
           <t>wer201213</t>
         </is>
       </c>
-      <c r="B259" s="3" t="n">
+      <c r="B259" s="2" t="n">
         <v>2012</v>
       </c>
-      <c r="C259" s="3" t="inlineStr">
+      <c r="C259" s="2" t="inlineStr">
         <is>
           <t>WER2012</t>
         </is>
       </c>
-      <c r="D259" s="3" t="inlineStr">
+      <c r="D259" s="2" t="inlineStr">
         <is>
           <t>15th Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E259" s="3" t="inlineStr">
+      <c r="E259" s="2" t="inlineStr">
         <is>
           <t>Buenos Aires, Argentina, 24-27 April 2012</t>
         </is>
       </c>
-      <c r="F259" s="3" t="inlineStr">
+      <c r="F259" s="2" t="inlineStr">
         <is>
           <t>Papers</t>
         </is>
       </c>
-      <c r="G259" s="3" t="inlineStr">
+      <c r="G259" s="2" t="inlineStr">
         <is>
           <t>Uma Apoio Sistematizado à Implementação do Processo de Desenvolvimento de Requisitos do MPS.BR e CMMI a partir do Uso de Ferramentas de Software Livre</t>
         </is>
       </c>
-      <c r="H259" s="3" t="inlineStr">
+      <c r="H259" s="2" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Ewelton Y. C. Yoshidome; Maurício R. de A. Souza; Wallace M. P. Lira; Sandro R. B. Oliveira; </t>
@@ -24652,63 +24708,63 @@
           <r>
             <rPr>
               <b val="1"/>
-              <color rgb="00C00000"/>
+              <color rgb="009C5700"/>
             </rPr>
             <t>Alexandre M. L. de Vasconcelos</t>
           </r>
         </is>
       </c>
-      <c r="I259" s="3" t="inlineStr">
+      <c r="I259" s="2" t="inlineStr">
         <is>
           <t>Ewelton Y. C. Yoshidome; Maurício R. de A. Souza; Wallace M. P. Lira; Sandro R. B. Oliveira; Alexandre Marcos Lins de Vasconcelos</t>
         </is>
       </c>
-      <c r="J259" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="K259" s="3" t="inlineStr">
-        <is>
-          <t>Alexandre M. L. de Vasconcelos → Alexandre Marcos Lins de Vasconcelos [revisar: subset]</t>
-        </is>
-      </c>
-      <c r="L259" s="3" t="n">
+      <c r="J259" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K259" s="2" t="inlineStr">
+        <is>
+          <t>Alexandre M. L. de Vasconcelos → Alexandre Marcos Lins de Vasconcelos [manual]</t>
+        </is>
+      </c>
+      <c r="L259" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="M259" s="3" t="inlineStr">
+      <c r="M259" s="2" t="inlineStr">
         <is>
           <t>To meet the market demands and ensure competitiveness, the search for quality has become a strategic goal for many companies, so the search for quality models becomes necessity. In this context, this paper proposes a tool support for implementation of Requirements Development process included in MPS.BR and CMMI programs, exclusively using free software tools, analyzing adherence to the maturity programs and trying to reduce the time and cost of its implementation.</t>
         </is>
       </c>
-      <c r="N259" s="3" t="inlineStr">
+      <c r="N259" s="2" t="inlineStr">
         <is>
           <t>Software Quality; MPS.BR; CMMI; Requirements Development; Free Software Tools.</t>
         </is>
       </c>
-      <c r="O259" s="3" t="inlineStr"/>
-      <c r="P259" s="3" t="inlineStr">
+      <c r="O259" s="2" t="inlineStr"/>
+      <c r="P259" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER2012/paper_9.pdf</t>
         </is>
       </c>
-      <c r="Q259" s="3" t="inlineStr">
+      <c r="Q259" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER2012/wer201213.html</t>
         </is>
       </c>
-      <c r="R259" s="3" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S259" s="3" t="inlineStr">
+      <c r="R259" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S259" s="2" t="inlineStr">
         <is>
           <t>978-987-1635-46-7</t>
         </is>
       </c>
-      <c r="T259" s="3" t="inlineStr"/>
-      <c r="U259" s="3" t="b">
+      <c r="T259" s="2" t="inlineStr"/>
+      <c r="U259" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -28793,40 +28849,40 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="3" t="inlineStr">
+      <c r="A304" s="2" t="inlineStr">
         <is>
           <t>wer201604</t>
         </is>
       </c>
-      <c r="B304" s="3" t="n">
+      <c r="B304" s="2" t="n">
         <v>2016</v>
       </c>
-      <c r="C304" s="3" t="inlineStr">
+      <c r="C304" s="2" t="inlineStr">
         <is>
           <t>WER2016</t>
         </is>
       </c>
-      <c r="D304" s="3" t="inlineStr">
+      <c r="D304" s="2" t="inlineStr">
         <is>
           <t>19th Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E304" s="3" t="inlineStr">
+      <c r="E304" s="2" t="inlineStr">
         <is>
           <t>Quito, Ecuador, 27-29 April 2016</t>
         </is>
       </c>
-      <c r="F304" s="3" t="inlineStr">
+      <c r="F304" s="2" t="inlineStr">
         <is>
           <t>Goal Oriented Requirements Engineering</t>
         </is>
       </c>
-      <c r="G304" s="3" t="inlineStr">
+      <c r="G304" s="2" t="inlineStr">
         <is>
           <t>Uma solução baseada em ontologia para o tratamento de erros em modelos construídos na linguagem i*</t>
         </is>
       </c>
-      <c r="H304" s="3" t="inlineStr">
+      <c r="H304" s="2" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Heyde Francielle do Carmo França; </t>
@@ -28834,59 +28890,59 @@
           <r>
             <rPr>
               <b val="1"/>
-              <color rgb="00C00000"/>
+              <color rgb="009C5700"/>
             </rPr>
             <t>Renato de Freitas Bulcão Neto</t>
           </r>
         </is>
       </c>
-      <c r="I304" s="3" t="inlineStr">
+      <c r="I304" s="2" t="inlineStr">
         <is>
           <t>Heyde Francielle do Carmo França; Renato F. Bulcão-Neto</t>
         </is>
       </c>
-      <c r="J304" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="K304" s="3" t="inlineStr">
-        <is>
-          <t>Renato de Freitas Bulcão Neto → Renato F. Bulcão-Neto [revisar: subset]</t>
-        </is>
-      </c>
-      <c r="L304" s="3" t="n">
+      <c r="J304" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K304" s="2" t="inlineStr">
+        <is>
+          <t>Renato de Freitas Bulcão Neto → Renato F. Bulcão-Neto [manual]</t>
+        </is>
+      </c>
+      <c r="L304" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M304" s="3" t="inlineStr">
+      <c r="M304" s="2" t="inlineStr">
         <is>
           <t>The i* language faces problems regarding the quality of requirements models, which include typical mistakes of misuse of its constructs, the presence of ambiguities on the interpretation of those constructs and the complexity of the resulting i* models. This paper proposes the extension of an ontology-based representation for i* models aiming at preventing the most well-known errors while constructing such models. Results demonstrate an approximate coverage of 70% of those common errors in the context of a case study.</t>
         </is>
       </c>
-      <c r="N304" s="3" t="inlineStr">
+      <c r="N304" s="2" t="inlineStr">
         <is>
           <t>Requirements Engineering; Goal; i* Language; OntoiStar; OWL.</t>
         </is>
       </c>
-      <c r="O304" s="3" t="inlineStr"/>
-      <c r="P304" s="3" t="inlineStr">
+      <c r="O304" s="2" t="inlineStr"/>
+      <c r="P304" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER2016/WER_2016_paper_43.pdf</t>
         </is>
       </c>
-      <c r="Q304" s="3" t="inlineStr">
+      <c r="Q304" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER2016/wer201604.html</t>
         </is>
       </c>
-      <c r="R304" s="3" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S304" s="3" t="inlineStr"/>
-      <c r="T304" s="3" t="inlineStr"/>
-      <c r="U304" s="3" t="b">
+      <c r="R304" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S304" s="2" t="inlineStr"/>
+      <c r="T304" s="2" t="inlineStr"/>
+      <c r="U304" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -32446,40 +32502,40 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="3" t="inlineStr">
+      <c r="A342" s="2" t="inlineStr">
         <is>
           <t>wer201815</t>
         </is>
       </c>
-      <c r="B342" s="3" t="n">
+      <c r="B342" s="2" t="n">
         <v>2018</v>
       </c>
-      <c r="C342" s="3" t="inlineStr">
+      <c r="C342" s="2" t="inlineStr">
         <is>
           <t>WER2018</t>
         </is>
       </c>
-      <c r="D342" s="3" t="inlineStr">
+      <c r="D342" s="2" t="inlineStr">
         <is>
           <t>21st Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E342" s="3" t="inlineStr">
+      <c r="E342" s="2" t="inlineStr">
         <is>
           <t>Rio de Janeiro, Brazil, 05-06 September 2018</t>
         </is>
       </c>
-      <c r="F342" s="3" t="inlineStr">
+      <c r="F342" s="2" t="inlineStr">
         <is>
           <t>Quality Requirements and Prioritization</t>
         </is>
       </c>
-      <c r="G342" s="3" t="inlineStr">
+      <c r="G342" s="2" t="inlineStr">
         <is>
           <t>Mechanisms to Support Requirements Prioritization: A Systematic Mapping Review</t>
         </is>
       </c>
-      <c r="H342" s="3" t="inlineStr">
+      <c r="H342" s="2" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Cinthya Cavalcanti; Maria Lencastre; </t>
@@ -32487,7 +32543,7 @@
           <r>
             <rPr>
               <b val="1"/>
-              <color rgb="00C00000"/>
+              <color rgb="009C5700"/>
             </rPr>
             <t>Roberta Fagundes</t>
           </r>
@@ -32496,103 +32552,103 @@
           </r>
         </is>
       </c>
-      <c r="I342" s="3" t="inlineStr">
+      <c r="I342" s="2" t="inlineStr">
         <is>
           <t>Cinthya Cavalcanti; Maria Lencastre; Roberta Andrade de A. Fagundes; Taina Santos; Daniel Ferreira</t>
         </is>
       </c>
-      <c r="J342" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="K342" s="3" t="inlineStr">
-        <is>
-          <t>Roberta Fagundes → Roberta Andrade de A. Fagundes [revisar: subset]</t>
-        </is>
-      </c>
-      <c r="L342" s="3" t="n">
+      <c r="J342" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K342" s="2" t="inlineStr">
+        <is>
+          <t>Roberta Fagundes → Roberta Andrade de A. Fagundes [manual]</t>
+        </is>
+      </c>
+      <c r="L342" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="M342" s="3" t="inlineStr">
+      <c r="M342" s="2" t="inlineStr">
         <is>
           <t>Requirements prioritization is applied to identify which artifacts must be implemented first, in order to create a product that best satisfies the customers need by using the smallest number of resources. However, the task of prioritizing requirements is challenging and complex, and there is no well-defined set of mechanisms that help this activity. This article aims at identifying and analyzing the mechanisms to support the requirements prioritization. So, a systematic map-ping review was conducted. The result is a report that presents the different types of publications (journals, conference papers, thesis, book chapters), the published year, the supporting mechanisms, the phases of the requirements engineering pro-cess, and the prioritization techniques and tools used. It was observed that the prioritization requirements field is quite needy of mechanisms and tools that sup-port this activity, mainly that ones that provide visual resources.</t>
         </is>
       </c>
-      <c r="N342" s="3" t="inlineStr">
+      <c r="N342" s="2" t="inlineStr">
         <is>
           <t>Requirements engineering; requirements prioritization; supporting mechanisms; systematic mapping review.</t>
         </is>
       </c>
-      <c r="O342" s="3" t="inlineStr">
+      <c r="O342" s="2" t="inlineStr">
         <is>
           <t>10.17771/PUCRio.wer.inf2018-52</t>
         </is>
       </c>
-      <c r="P342" s="3" t="inlineStr">
+      <c r="P342" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER2018/WER_2018_paper_52.pdf</t>
         </is>
       </c>
-      <c r="Q342" s="3" t="inlineStr">
+      <c r="Q342" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER2018/wer201815.html</t>
         </is>
       </c>
-      <c r="R342" s="3" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S342" s="3" t="inlineStr">
+      <c r="R342" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S342" s="2" t="inlineStr">
         <is>
           <t>978-85-907171-1-9</t>
         </is>
       </c>
-      <c r="T342" s="3" t="inlineStr">
+      <c r="T342" s="2" t="inlineStr">
         <is>
           <t>Editora PUC-Rio</t>
         </is>
       </c>
-      <c r="U342" s="3" t="b">
+      <c r="U342" s="2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="3" t="inlineStr">
+      <c r="A343" s="2" t="inlineStr">
         <is>
           <t>wer201816</t>
         </is>
       </c>
-      <c r="B343" s="3" t="n">
+      <c r="B343" s="2" t="n">
         <v>2018</v>
       </c>
-      <c r="C343" s="3" t="inlineStr">
+      <c r="C343" s="2" t="inlineStr">
         <is>
           <t>WER2018</t>
         </is>
       </c>
-      <c r="D343" s="3" t="inlineStr">
+      <c r="D343" s="2" t="inlineStr">
         <is>
           <t>21st Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E343" s="3" t="inlineStr">
+      <c r="E343" s="2" t="inlineStr">
         <is>
           <t>Rio de Janeiro, Brazil, 05-06 September 2018</t>
         </is>
       </c>
-      <c r="F343" s="3" t="inlineStr">
+      <c r="F343" s="2" t="inlineStr">
         <is>
           <t>Quality Requirements and Prioritization</t>
         </is>
       </c>
-      <c r="G343" s="3" t="inlineStr">
+      <c r="G343" s="2" t="inlineStr">
         <is>
           <t>Priorização de Requisitos em Startups no Armazém da Criatividade (Porto Digital): Resultados Preliminares</t>
         </is>
       </c>
-      <c r="H343" s="3" t="inlineStr">
+      <c r="H343" s="2" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Gustavo Silva; </t>
@@ -32600,7 +32656,7 @@
           <r>
             <rPr>
               <b val="1"/>
-              <color rgb="00C00000"/>
+              <color rgb="009C5700"/>
             </rPr>
             <t>Wylliams Santos</t>
           </r>
@@ -32609,65 +32665,65 @@
           </r>
         </is>
       </c>
-      <c r="I343" s="3" t="inlineStr">
+      <c r="I343" s="2" t="inlineStr">
         <is>
           <t>Gustavo Silva; Wylliams Barbosa Santos; Maria Lencastre</t>
         </is>
       </c>
-      <c r="J343" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="K343" s="3" t="inlineStr">
-        <is>
-          <t>Wylliams Santos → Wylliams Barbosa Santos [revisar: subset]</t>
-        </is>
-      </c>
-      <c r="L343" s="3" t="n">
+      <c r="J343" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K343" s="2" t="inlineStr">
+        <is>
+          <t>Wylliams Santos → Wylliams Barbosa Santos [manual]</t>
+        </is>
+      </c>
+      <c r="L343" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M343" s="3" t="inlineStr">
+      <c r="M343" s="2" t="inlineStr">
         <is>
           <t>As startups de software vêm ganhando destaque no mercado; na maioria das vezes, estão associadas ao conceito de desenvolvimento de produtos de software inovadores e que lidam com limitações de tempo e recursos. Pesquisas apontam que as startups não são versões menores de grandes empresas e que as práticas existentes de desenvolvimento de software não podem ser repassadas diretamente para as startups sem os devidos ajustes. Poucos estudos abordam e exploram como a priorização de requisitos é praticada em startups. Apesar de ser uma atividade essencial para garantir o sucesso dos projetos, isto é, para satisfazer às necessidades mais importantes e críticas dos stakeholders, assim como para o planejamento de releases. O objetivo deste artigo é explorar através de um estudo qualitativo as práticas de priorização de requisitos utilizadas em startups e os desafios associados a essas práticas. Com isso, será obtido conhecimento que poderá fortalecer novas pesquisas relacionadas à priorização de requisitos no contexto de startups, permitindo auxiliar também profissionais com a intenção de iniciar startups de software.</t>
         </is>
       </c>
-      <c r="N343" s="3" t="inlineStr">
+      <c r="N343" s="2" t="inlineStr">
         <is>
           <t>Engenharia de Requisitos; priorização de requisitos; startups</t>
         </is>
       </c>
-      <c r="O343" s="3" t="inlineStr">
+      <c r="O343" s="2" t="inlineStr">
         <is>
           <t>10.17771/PUCRio.wer.inf2018-58</t>
         </is>
       </c>
-      <c r="P343" s="3" t="inlineStr">
+      <c r="P343" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER2018/WER_2018_paper_58.pdf</t>
         </is>
       </c>
-      <c r="Q343" s="3" t="inlineStr">
+      <c r="Q343" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER2018/wer201816.html</t>
         </is>
       </c>
-      <c r="R343" s="3" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S343" s="3" t="inlineStr">
+      <c r="R343" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S343" s="2" t="inlineStr">
         <is>
           <t>978-85-907171-1-9</t>
         </is>
       </c>
-      <c r="T343" s="3" t="inlineStr">
+      <c r="T343" s="2" t="inlineStr">
         <is>
           <t>Editora PUC-Rio</t>
         </is>
       </c>
-      <c r="U343" s="3" t="b">
+      <c r="U343" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -39585,40 +39641,40 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="3" t="inlineStr">
+      <c r="A412" s="2" t="inlineStr">
         <is>
           <t>wer202125</t>
         </is>
       </c>
-      <c r="B412" s="3" t="n">
+      <c r="B412" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="C412" s="3" t="inlineStr">
+      <c r="C412" s="2" t="inlineStr">
         <is>
           <t>WER2021</t>
         </is>
       </c>
-      <c r="D412" s="3" t="inlineStr">
+      <c r="D412" s="2" t="inlineStr">
         <is>
           <t>24th Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E412" s="3" t="inlineStr">
+      <c r="E412" s="2" t="inlineStr">
         <is>
           <t>Brasilia, DF, Brazil, 23-27 August 2021</t>
         </is>
       </c>
-      <c r="F412" s="3" t="inlineStr">
+      <c r="F412" s="2" t="inlineStr">
         <is>
           <t>Masters and Doctoral Thesis Track</t>
         </is>
       </c>
-      <c r="G412" s="3" t="inlineStr">
+      <c r="G412" s="2" t="inlineStr">
         <is>
           <t>Mantendo a consistência na coevolução de modelos iStar, BPMN e Casos de Uso na Engenharia de Requisitos</t>
         </is>
       </c>
-      <c r="H412" s="3" t="inlineStr">
+      <c r="H412" s="2" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Diogo Do Nascimento Paza; </t>
@@ -39626,71 +39682,71 @@
           <r>
             <rPr>
               <b val="1"/>
-              <color rgb="00C00000"/>
+              <color rgb="009C5700"/>
             </rPr>
             <t>Victor Santander</t>
           </r>
         </is>
       </c>
-      <c r="I412" s="3" t="inlineStr">
+      <c r="I412" s="2" t="inlineStr">
         <is>
           <t>Diogo Do Nascimento Paza; Victor Francisco Araya Santander</t>
         </is>
       </c>
-      <c r="J412" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="K412" s="3" t="inlineStr">
-        <is>
-          <t>Victor Santander → Victor Francisco Araya Santander [revisar: subset]</t>
-        </is>
-      </c>
-      <c r="L412" s="3" t="n">
+      <c r="J412" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K412" s="2" t="inlineStr">
+        <is>
+          <t>Victor Santander → Victor Francisco Araya Santander [manual]</t>
+        </is>
+      </c>
+      <c r="L412" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M412" s="3" t="inlineStr">
+      <c r="M412" s="2" t="inlineStr">
         <is>
           <t>A Engenharia de Requisitos (ER)  é uma etapa fundamental no desenvolvimento de um software. Tecnicas de modelagem organizacional  como iStar (lê-se i-estrela), de processos de negócio como BPMN (Business Process Model and Notation) e de requisitos funcionais como Caso de uso UML são utilizadas para elicitar e documentar requisitos. Em trabalhos prévios, propõe-se derivar casos de uso a partir de modelos iStar e BPMN e gerar esses artefatos na ferramenta JGOOSE (Java Goal into Object Oriented Standard Extension). Contudo, as diretrizes de derivação propostas e a ferramenta de suporte não garantem a consistência desses artefatos quando os mesmos evoluem. Isto significa que altera¸cões em casos de uso não são refletidas nos modelos iStar ou BPMN usados como base. Esta deficiência pode levar à documentos inconsistentes ao longo do ciclo de vida de um software. Desta forma, propõe-se definir regras de mapeamento que garantam a consistência entre esses modelos bem como incluir esse suporte na ferramenta JGOOSE. Também neste trabalho pretende-se validar a solução proposta utilizando a engenharia de software experimental.</t>
         </is>
       </c>
-      <c r="N412" s="3" t="inlineStr">
+      <c r="N412" s="2" t="inlineStr">
         <is>
           <t>iStar; framework i*; i-estrela; BPMN; Casos de Uso; Modelagem UML; Modelos de Negócio; Modelos Organizacionais</t>
         </is>
       </c>
-      <c r="O412" s="3" t="inlineStr">
+      <c r="O412" s="2" t="inlineStr">
         <is>
           <t>10.29327/1298728.24-25</t>
         </is>
       </c>
-      <c r="P412" s="3" t="inlineStr">
+      <c r="P412" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER2021/WER_2021_paper_7.pdf</t>
         </is>
       </c>
-      <c r="Q412" s="3" t="inlineStr">
+      <c r="Q412" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER2021/wer202125.html</t>
         </is>
       </c>
-      <c r="R412" s="3" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S412" s="3" t="inlineStr">
+      <c r="R412" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S412" s="2" t="inlineStr">
         <is>
           <t>978-65-00-73407-2</t>
         </is>
       </c>
-      <c r="T412" s="3" t="inlineStr">
+      <c r="T412" s="2" t="inlineStr">
         <is>
           <t>Even3, Brazil</t>
         </is>
       </c>
-      <c r="U412" s="3" t="b">
+      <c r="U412" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -39822,40 +39878,40 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="3" t="inlineStr">
+      <c r="A414" s="2" t="inlineStr">
         <is>
           <t>wer202127</t>
         </is>
       </c>
-      <c r="B414" s="3" t="n">
+      <c r="B414" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="C414" s="3" t="inlineStr">
+      <c r="C414" s="2" t="inlineStr">
         <is>
           <t>WER2021</t>
         </is>
       </c>
-      <c r="D414" s="3" t="inlineStr">
+      <c r="D414" s="2" t="inlineStr">
         <is>
           <t>24th Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E414" s="3" t="inlineStr">
+      <c r="E414" s="2" t="inlineStr">
         <is>
           <t>Brasilia, DF, Brazil, 23-27 August 2021</t>
         </is>
       </c>
-      <c r="F414" s="3" t="inlineStr">
+      <c r="F414" s="2" t="inlineStr">
         <is>
           <t>Masters and Doctoral Thesis Track</t>
         </is>
       </c>
-      <c r="G414" s="3" t="inlineStr">
+      <c r="G414" s="2" t="inlineStr">
         <is>
           <t>Processo de Especificação de Banco de Dados em Sistemas Críticos</t>
         </is>
       </c>
-      <c r="H414" s="3" t="inlineStr">
+      <c r="H414" s="2" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Sarasuaty Yelisetty; </t>
@@ -39863,7 +39919,7 @@
           <r>
             <rPr>
               <b val="1"/>
-              <color rgb="00C00000"/>
+              <color rgb="009C5700"/>
             </rPr>
             <t>Johnny Marques</t>
           </r>
@@ -39872,65 +39928,65 @@
           </r>
         </is>
       </c>
-      <c r="I414" s="3" t="inlineStr">
+      <c r="I414" s="2" t="inlineStr">
         <is>
           <t>Sarasuaty Yelisetty; Johnny Cardoso Marques; Luiz Dias</t>
         </is>
       </c>
-      <c r="J414" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="K414" s="3" t="inlineStr">
-        <is>
-          <t>Johnny Marques → Johnny Cardoso Marques [revisar: subset]</t>
-        </is>
-      </c>
-      <c r="L414" s="3" t="n">
+      <c r="J414" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K414" s="2" t="inlineStr">
+        <is>
+          <t>Johnny Marques → Johnny Cardoso Marques [manual]</t>
+        </is>
+      </c>
+      <c r="L414" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M414" s="3" t="inlineStr">
+      <c r="M414" s="2" t="inlineStr">
         <is>
           <t>O software de sistemas críticos em segurança, incluindo banco de dados, requer processos robustos de especificação, desenvolvimento, validação, verificação, gerenciamento de configuração e garantia de qualidade.  A pesquisa reportada neste trabalho, em seu estágio atual, propõe a criação de um processo de especificação e validação de requisitos para bancos de dados em sistemas críticos. A metodologia utilizada envolve a condução de uma Revisão Sistemática da Literatura em processos de especificação de bancos de dados. Adicionalmente, inclui-se um diagrama do processo de especificação e validação de requisitos para bancos de dados  em sistemas críticos que inclui a criação dos cenários de validação de requisitos. Espera-se que o processo possa ser utilizado por empresas desenvolvedoras de sistemas críticos e apresentará rastreabilidade para as necessidades regulatórias de alguns domínios selecionados como o aeronáutico, médico e ferroviário. Adicionalmente, o processo também permitirá uma construção organizada de bancos de dados orientados por requisitos, visando a mitigação de erros inseridos em sua construção e mecanismos de garantias desde a especificação até a integração com o software de aplicação.</t>
         </is>
       </c>
-      <c r="N414" s="3" t="inlineStr">
+      <c r="N414" s="2" t="inlineStr">
         <is>
           <t>banco de dados; sistemas críticos; requisito; processo; validação</t>
         </is>
       </c>
-      <c r="O414" s="3" t="inlineStr">
+      <c r="O414" s="2" t="inlineStr">
         <is>
           <t>10.29327/1298728.24-26</t>
         </is>
       </c>
-      <c r="P414" s="3" t="inlineStr">
+      <c r="P414" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER2021/WER_2021_paper_21.pdf</t>
         </is>
       </c>
-      <c r="Q414" s="3" t="inlineStr">
+      <c r="Q414" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER2021/wer202127.html</t>
         </is>
       </c>
-      <c r="R414" s="3" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S414" s="3" t="inlineStr">
+      <c r="R414" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S414" s="2" t="inlineStr">
         <is>
           <t>978-65-00-73407-2</t>
         </is>
       </c>
-      <c r="T414" s="3" t="inlineStr">
+      <c r="T414" s="2" t="inlineStr">
         <is>
           <t>Even3, Brazil</t>
         </is>
       </c>
-      <c r="U414" s="3" t="b">
+      <c r="U414" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -40032,40 +40088,40 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="3" t="inlineStr">
+      <c r="A416" s="2" t="inlineStr">
         <is>
           <t>wer202200</t>
         </is>
       </c>
-      <c r="B416" s="3" t="n">
+      <c r="B416" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="C416" s="3" t="inlineStr">
+      <c r="C416" s="2" t="inlineStr">
         <is>
           <t>WER2022</t>
         </is>
       </c>
-      <c r="D416" s="3" t="inlineStr">
+      <c r="D416" s="2" t="inlineStr">
         <is>
           <t>25th Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E416" s="3" t="inlineStr">
+      <c r="E416" s="2" t="inlineStr">
         <is>
           <t>Virtual mode, Natal, RN, Brazil, 23-26 August 2022</t>
         </is>
       </c>
-      <c r="F416" s="3" t="inlineStr">
+      <c r="F416" s="2" t="inlineStr">
         <is>
           <t>Preface</t>
         </is>
       </c>
-      <c r="G416" s="3" t="inlineStr">
+      <c r="G416" s="2" t="inlineStr">
         <is>
           <t>Preface: Proceedings of the Workshop on Requirements Engineering (WER2022)</t>
         </is>
       </c>
-      <c r="H416" s="3" t="inlineStr">
+      <c r="H416" s="2" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Leandro Antonelli; Maria Lencastre; </t>
@@ -40073,71 +40129,71 @@
           <r>
             <rPr>
               <b val="1"/>
-              <color rgb="00C00000"/>
+              <color rgb="009C5700"/>
             </rPr>
             <t>Victor Santander</t>
           </r>
         </is>
       </c>
-      <c r="I416" s="3" t="inlineStr">
+      <c r="I416" s="2" t="inlineStr">
         <is>
           <t>Leandro Antonelli; Maria Lencastre; Victor Francisco Araya Santander</t>
         </is>
       </c>
-      <c r="J416" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="K416" s="3" t="inlineStr">
-        <is>
-          <t>Victor Santander → Victor Francisco Araya Santander [revisar: subset]</t>
-        </is>
-      </c>
-      <c r="L416" s="3" t="n">
+      <c r="J416" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K416" s="2" t="inlineStr">
+        <is>
+          <t>Victor Santander → Victor Francisco Araya Santander [manual]</t>
+        </is>
+      </c>
+      <c r="L416" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M416" s="3" t="inlineStr">
+      <c r="M416" s="2" t="inlineStr">
         <is>
           <t>The 25th Workshop on Requirements Engineering (WER 2022) was held at the Federal University of Rio Grande do Norte (UFRN) in Natal, Brazil, from August 23rd to 26th. The event marked a milestone in the WER series and brought together a diverse international community to discuss key challenges in Requirements Engineering. Featuring keynote talks from prominent researchers such as Daniel Amyot, Luis Olsina, Luiz Marcio Cysneiros, and Óscar Pastor, the program spanned multiple tracks including Research, Journal First, Tools, and Master's and Doctoral sessions. Highlights included industry talks on real-world requirements in public health systems, a tutorial on security requirements elicitation, and a retrospective panel celebrating 25 years of WER. The open-access proceedings showcased innovative work on privacy, design thinking, machine learning, and safety requirements, reflecting the event’s commitment to academic excellence and industry relevance.</t>
         </is>
       </c>
-      <c r="N416" s="3" t="inlineStr">
+      <c r="N416" s="2" t="inlineStr">
         <is>
           <t>wer; Requirements Engineering</t>
         </is>
       </c>
-      <c r="O416" s="3" t="inlineStr">
+      <c r="O416" s="2" t="inlineStr">
         <is>
           <t>10.29327/1298262.25-1</t>
         </is>
       </c>
-      <c r="P416" s="3" t="inlineStr">
+      <c r="P416" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER2022/WER2022_preface.pdf</t>
         </is>
       </c>
-      <c r="Q416" s="3" t="inlineStr">
+      <c r="Q416" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER2022/wer202200.html</t>
         </is>
       </c>
-      <c r="R416" s="3" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S416" s="3" t="inlineStr">
+      <c r="R416" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S416" s="2" t="inlineStr">
         <is>
           <t>978-65-00-73495-9</t>
         </is>
       </c>
-      <c r="T416" s="3" t="inlineStr">
+      <c r="T416" s="2" t="inlineStr">
         <is>
           <t>Even3, Brazil</t>
         </is>
       </c>
-      <c r="U416" s="3" t="b">
+      <c r="U416" s="2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -40239,40 +40295,40 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="3" t="inlineStr">
+      <c r="A418" s="2" t="inlineStr">
         <is>
           <t>wer202202</t>
         </is>
       </c>
-      <c r="B418" s="3" t="n">
+      <c r="B418" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="C418" s="3" t="inlineStr">
+      <c r="C418" s="2" t="inlineStr">
         <is>
           <t>WER2022</t>
         </is>
       </c>
-      <c r="D418" s="3" t="inlineStr">
+      <c r="D418" s="2" t="inlineStr">
         <is>
           <t>25th Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E418" s="3" t="inlineStr">
+      <c r="E418" s="2" t="inlineStr">
         <is>
           <t>Virtual mode, Natal, RN, Brazil, 23-26 August 2022</t>
         </is>
       </c>
-      <c r="F418" s="3" t="inlineStr">
+      <c r="F418" s="2" t="inlineStr">
         <is>
           <t>Research Track - Full papers</t>
         </is>
       </c>
-      <c r="G418" s="3" t="inlineStr">
+      <c r="G418" s="2" t="inlineStr">
         <is>
           <t>A Catalogue of KAOS Extensions</t>
         </is>
       </c>
-      <c r="H418" s="3" t="inlineStr">
+      <c r="H418" s="2" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Pedro Rodrigues de Carvalho Junior; </t>
@@ -40280,7 +40336,7 @@
           <r>
             <rPr>
               <b val="1"/>
-              <color rgb="00C00000"/>
+              <color rgb="009C5700"/>
             </rPr>
             <t>Enyo José Tavares Gonçalves</t>
           </r>
@@ -40289,65 +40345,65 @@
           </r>
         </is>
       </c>
-      <c r="I418" s="3" t="inlineStr">
+      <c r="I418" s="2" t="inlineStr">
         <is>
           <t>Pedro Rodrigues de Carvalho Junior; Enyo Gonçalves; Rainara Maia Carvalho; Marcos Antonio de Oliveira</t>
         </is>
       </c>
-      <c r="J418" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="K418" s="3" t="inlineStr">
-        <is>
-          <t>Enyo José Tavares Gonçalves → Enyo Gonçalves [revisar: subset]</t>
-        </is>
-      </c>
-      <c r="L418" s="3" t="n">
+      <c r="J418" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K418" s="2" t="inlineStr">
+        <is>
+          <t>Enyo José Tavares Gonçalves → Enyo Gonçalves [manual]</t>
+        </is>
+      </c>
+      <c r="L418" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="M418" s="3" t="inlineStr">
+      <c r="M418" s="2" t="inlineStr">
         <is>
           <t>KAOS, a goal-based modeling language, has been extended since its creation. Searching for existing KAOS extensions and their constructs is a task that can be the start point for requirements modeling or for the creation of new KAOS extensions. This search can be performed by using strings searches in databases or through a catalogue that supports them. This exploratory task about extensions can take a great deal of time and be prone to failure when performed without specific and adequate support. catalogues have been used successfully to bring together a body of knowledge, including knowledge of modeling language extensions. Motivated by this scenario, this work proposes a catalogue of extensions to the KAOS modeling language. The results suggest that the proposed catalogue can be used to retrieve information about extensions and their constructs correctly and that it is easy to use.</t>
         </is>
       </c>
-      <c r="N418" s="3" t="inlineStr">
+      <c r="N418" s="2" t="inlineStr">
         <is>
           <t>Requirements Engineering; KAOS; Extensions; Catalogue</t>
         </is>
       </c>
-      <c r="O418" s="3" t="inlineStr">
+      <c r="O418" s="2" t="inlineStr">
         <is>
           <t>10.29327/1298262.25-9</t>
         </is>
       </c>
-      <c r="P418" s="3" t="inlineStr">
+      <c r="P418" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER2022/WER_2022_Camera_ready_paper_29.pdf</t>
         </is>
       </c>
-      <c r="Q418" s="3" t="inlineStr">
+      <c r="Q418" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER2022/wer202202.html</t>
         </is>
       </c>
-      <c r="R418" s="3" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S418" s="3" t="inlineStr">
+      <c r="R418" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S418" s="2" t="inlineStr">
         <is>
           <t>978-65-00-73495-9</t>
         </is>
       </c>
-      <c r="T418" s="3" t="inlineStr">
+      <c r="T418" s="2" t="inlineStr">
         <is>
           <t>Even3, Brazil</t>
         </is>
       </c>
-      <c r="U418" s="3" t="b">
+      <c r="U418" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -40829,13 +40885,20 @@
             <t>Victor A. Pozzan</t>
           </r>
           <r>
-            <t>; Marco A. Toranzo Céspedes</t>
+            <t xml:space="preserve">; </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="009C5700"/>
+            </rPr>
+            <t>Marco A. Toranzo Céspedes</t>
           </r>
         </is>
       </c>
       <c r="I423" s="2" t="inlineStr">
         <is>
-          <t>Victor Francisco Araya Santander; Sidgley C. de Andrade; Ivonei Freitas da Silva; Alexandre Luiz de Borba Silva; Victor Augusto Pozzan; Marco A. Toranzo Céspedes</t>
+          <t>Victor Francisco Araya Santander; Sidgley C. de Andrade; Ivonei Freitas da Silva; Alexandre Luiz de Borba Silva; Victor Augusto Pozzan; Marco Toranzo</t>
         </is>
       </c>
       <c r="J423" s="2" t="inlineStr">
@@ -40845,7 +40908,7 @@
       </c>
       <c r="K423" s="2" t="inlineStr">
         <is>
-          <t>Victor F.A. Santander → Victor Francisco Araya Santander [subset]; Ivonei F. da Silva → Ivonei Freitas da Silva [subset]; Alexandre L. B. Silva → Alexandre Luiz de Borba Silva [subset]; Victor A. Pozzan → Victor Augusto Pozzan [subset]</t>
+          <t>Victor F.A. Santander → Victor Francisco Araya Santander [subset]; Ivonei F. da Silva → Ivonei Freitas da Silva [subset]; Alexandre L. B. Silva → Alexandre Luiz de Borba Silva [subset]; Victor A. Pozzan → Victor Augusto Pozzan [subset]; Marco A. Toranzo Céspedes → Marco Toranzo [manual]</t>
         </is>
       </c>
       <c r="L423" s="2" t="n">
@@ -42988,40 +43051,40 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" s="3" t="inlineStr">
+      <c r="A445" s="2" t="inlineStr">
         <is>
           <t>wer202300</t>
         </is>
       </c>
-      <c r="B445" s="3" t="n">
+      <c r="B445" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="C445" s="3" t="inlineStr">
+      <c r="C445" s="2" t="inlineStr">
         <is>
           <t>WER2023</t>
         </is>
       </c>
-      <c r="D445" s="3" t="inlineStr">
+      <c r="D445" s="2" t="inlineStr">
         <is>
           <t>26th Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E445" s="3" t="inlineStr">
+      <c r="E445" s="2" t="inlineStr">
         <is>
           <t>Porto Alegre, RS, Brazil, 15-17 August 2023</t>
         </is>
       </c>
-      <c r="F445" s="3" t="inlineStr">
+      <c r="F445" s="2" t="inlineStr">
         <is>
           <t>Preface</t>
         </is>
       </c>
-      <c r="G445" s="3" t="inlineStr">
+      <c r="G445" s="2" t="inlineStr">
         <is>
           <t>Preface: Proceedings of the Workshop on Requirements Engineering (WER2023)</t>
         </is>
       </c>
-      <c r="H445" s="3" t="inlineStr">
+      <c r="H445" s="2" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Leandro Antonelli; Marcia Lucena; </t>
@@ -43029,71 +43092,71 @@
           <r>
             <rPr>
               <b val="1"/>
-              <color rgb="00C00000"/>
+              <color rgb="009C5700"/>
             </rPr>
             <t>Roxana L.Q. Portugal</t>
           </r>
         </is>
       </c>
-      <c r="I445" s="3" t="inlineStr">
+      <c r="I445" s="2" t="inlineStr">
         <is>
           <t>Leandro Antonelli; Marcia Lucena; Roxana Portugal</t>
         </is>
       </c>
-      <c r="J445" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="K445" s="3" t="inlineStr">
-        <is>
-          <t>Roxana L.Q. Portugal → Roxana Portugal [revisar: subset]</t>
-        </is>
-      </c>
-      <c r="L445" s="3" t="n">
+      <c r="J445" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K445" s="2" t="inlineStr">
+        <is>
+          <t>Roxana L.Q. Portugal → Roxana Portugal [manual]</t>
+        </is>
+      </c>
+      <c r="L445" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M445" s="3" t="inlineStr">
+      <c r="M445" s="2" t="inlineStr">
         <is>
           <t>The twenty-sixth edition of the Requirements Engineering Workshop, held at PUC-RS in Porto Alegre, Brazil from August 15th to 17th, 2023, fostered vibrant discussions bridging academia and industry. Over three days, participants explored multifaceted topics including Usability, Transparency, Data Protection, Smart Cities, Safety Requirements, Modeling, and Knowledge Management Requirements. With 26 submissions and rigorous reviews, 11 full papers and 6 short papers were accepted. The event paid tribute to Professor Luiz Márcio Cysneiros and featured keynotes by Professors Ricardo Gaucitua and Juliana Saraiva. Engaging panel discussions centered on industry-academia synergy illuminated shared challenges and the potential for collaborative initiatives. Notably, a dedicated industry track was introduced, and Luciane Forte from Globo presented insights into Big Brother Brazil's voting platform requirements. The workshop's success was a result of international collaboration, paper contributors, organizers, and engaged participants, all committed to advancing the realm of Requirements Engineering.</t>
         </is>
       </c>
-      <c r="N445" s="3" t="inlineStr">
+      <c r="N445" s="2" t="inlineStr">
         <is>
           <t>wer; Requirements Engineering</t>
         </is>
       </c>
-      <c r="O445" s="3" t="inlineStr">
+      <c r="O445" s="2" t="inlineStr">
         <is>
           <t>10.29327/1298356.26-26</t>
         </is>
       </c>
-      <c r="P445" s="3" t="inlineStr">
+      <c r="P445" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER2023/preface_23.pdf</t>
         </is>
       </c>
-      <c r="Q445" s="3" t="inlineStr">
+      <c r="Q445" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER2023/wer202300.html</t>
         </is>
       </c>
-      <c r="R445" s="3" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S445" s="3" t="inlineStr">
+      <c r="R445" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S445" s="2" t="inlineStr">
         <is>
           <t>978-65-00-77516-7</t>
         </is>
       </c>
-      <c r="T445" s="3" t="inlineStr">
+      <c r="T445" s="2" t="inlineStr">
         <is>
           <t>Even3, Brazil</t>
         </is>
       </c>
-      <c r="U445" s="3" t="b">
+      <c r="U445" s="2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -43599,112 +43662,103 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" s="3" t="inlineStr">
+      <c r="A451" s="2" t="inlineStr">
         <is>
           <t>wer202306</t>
         </is>
       </c>
-      <c r="B451" s="3" t="n">
+      <c r="B451" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="C451" s="3" t="inlineStr">
+      <c r="C451" s="2" t="inlineStr">
         <is>
           <t>WER2023</t>
         </is>
       </c>
-      <c r="D451" s="3" t="inlineStr">
+      <c r="D451" s="2" t="inlineStr">
         <is>
           <t>26th Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E451" s="3" t="inlineStr">
+      <c r="E451" s="2" t="inlineStr">
         <is>
           <t>Porto Alegre, RS, Brazil, 15-17 August 2023</t>
         </is>
       </c>
-      <c r="F451" s="3" t="inlineStr">
+      <c r="F451" s="2" t="inlineStr">
         <is>
           <t>Research Track - Full Papers</t>
         </is>
       </c>
-      <c r="G451" s="3" t="inlineStr">
+      <c r="G451" s="2" t="inlineStr">
         <is>
           <t>ReQSI-CI: Um Catálogo de Requisitos Não-Funcionais para Sistemas de Informação em Cidades Inteligentes sob a Perspectiva de Ecossistemas Digitais</t>
         </is>
       </c>
-      <c r="H451" s="3" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Alexandre Barbosa; Paulo Malcher; </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00C00000"/>
-            </rPr>
-            <t>Rodrigo Santos</t>
-          </r>
-        </is>
-      </c>
-      <c r="I451" s="3" t="inlineStr">
+      <c r="H451" s="2" t="inlineStr">
         <is>
           <t>Alexandre Barbosa; Paulo Malcher; Rodrigo Santos</t>
         </is>
       </c>
-      <c r="J451" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="K451" s="3" t="inlineStr">
-        <is>
-          <t>Rodrigo Santos [revisar: ambiguous]</t>
-        </is>
-      </c>
-      <c r="L451" s="3" t="n">
+      <c r="I451" s="2" t="inlineStr">
+        <is>
+          <t>Alexandre Barbosa; Paulo Malcher; Rodrigo Pereira dos Santos</t>
+        </is>
+      </c>
+      <c r="J451" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K451" s="2" t="inlineStr">
+        <is>
+          <t>Rodrigo Santos → Rodrigo Pereira dos Santos [manual]</t>
+        </is>
+      </c>
+      <c r="L451" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M451" s="3" t="inlineStr">
+      <c r="M451" s="2" t="inlineStr">
         <is>
           <t>Iniciativas de cidades inteligentes (CI) vêm aumentando em todo mundo. Diante desse contexto, os sistemas de informação (SI) são vistos como ferramentas estratégicas para a solução de problemas a partir de uma visão sistêmica sobre pessoas, organizações e tecnologias. No entanto, vários SI têm sido usados para apoiar iniciativas de CI e não há uma diretriz específica ou padrão de requisitos que possa apoiar o desenvolvimento de SI. Este trabalho apresenta um catálogo de requisitos não-funcionais (RNF) de SI em CI sob a perspectiva de ecossistemas digitais (ED), chamado ReQSI-CI. A proposta de catálogo emergiu dos resultados de três estudos: (i) um estudo exploratório que identificou RNF por meio de oportunidades e barreiras na implantação de SI informais no domínio das CI; (ii) um mapeamento sistemático da literatura (MSL) que identificou SI formais, desafios e fatores de sucesso da implantação desses SI, que possibilitaram a identificação de RNF; e (iii) uma pesquisa de opinião que foi realizada com estudantes, pesquisadores e profissionais brasileiros interessados no tema, a fim de analisar as informações dos SI identificados no MSL e identificar novos RNF. Ao final, foi conduzida uma avaliação do catálogo por meio de um grupo focal com especialistas no assunto, resultando em uma nova versão do catálogo ReQSI-CI. Os resultados mostram que a proposta reúne elementos relevantes para CI, com destaque para características de ED. A contribuição deste trabalho é um catálogo com 46 RNF organizados em dimensões e domínios de CI.</t>
         </is>
       </c>
-      <c r="N451" s="3" t="inlineStr">
+      <c r="N451" s="2" t="inlineStr">
         <is>
           <t>Sistemas de Informação; Cidades Inteligentes; Requisitos Não-Funcionais; Ecossistemas Digitais</t>
         </is>
       </c>
-      <c r="O451" s="3" t="inlineStr">
+      <c r="O451" s="2" t="inlineStr">
         <is>
           <t>10.29327/1298356.26-9</t>
         </is>
       </c>
-      <c r="P451" s="3" t="inlineStr">
+      <c r="P451" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER2023/WER_2023_paper_10.pdf</t>
         </is>
       </c>
-      <c r="Q451" s="3" t="inlineStr">
+      <c r="Q451" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER2023/wer202306.html</t>
         </is>
       </c>
-      <c r="R451" s="3" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S451" s="3" t="inlineStr">
+      <c r="R451" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S451" s="2" t="inlineStr">
         <is>
           <t>978-65-00-77516-7</t>
         </is>
       </c>
-      <c r="T451" s="3" t="inlineStr">
+      <c r="T451" s="2" t="inlineStr">
         <is>
           <t>Even3, Brazil</t>
         </is>
       </c>
-      <c r="U451" s="3" t="b">
+      <c r="U451" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -48143,45 +48197,45 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496" s="3" t="inlineStr">
+      <c r="A496" s="2" t="inlineStr">
         <is>
           <t>wer202425</t>
         </is>
       </c>
-      <c r="B496" s="3" t="n">
+      <c r="B496" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="C496" s="3" t="inlineStr">
+      <c r="C496" s="2" t="inlineStr">
         <is>
           <t>WER2024</t>
         </is>
       </c>
-      <c r="D496" s="3" t="inlineStr">
+      <c r="D496" s="2" t="inlineStr">
         <is>
           <t>27th Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E496" s="3" t="inlineStr">
+      <c r="E496" s="2" t="inlineStr">
         <is>
           <t>Buenos Aires, Argentina, 7-9 August 2024</t>
         </is>
       </c>
-      <c r="F496" s="3" t="inlineStr">
+      <c r="F496" s="2" t="inlineStr">
         <is>
           <t>Industry Track</t>
         </is>
       </c>
-      <c r="G496" s="3" t="inlineStr">
+      <c r="G496" s="2" t="inlineStr">
         <is>
           <t>Implementing Accuracy Quality for Responsible AI in Newsrooms</t>
         </is>
       </c>
-      <c r="H496" s="3" t="inlineStr">
+      <c r="H496" s="2" t="inlineStr">
         <is>
           <r>
             <rPr>
               <b val="1"/>
-              <color rgb="00C00000"/>
+              <color rgb="009C5700"/>
             </rPr>
             <t>Roxana L.Q. Portugal</t>
           </r>
@@ -48190,65 +48244,65 @@
           </r>
         </is>
       </c>
-      <c r="I496" s="3" t="inlineStr">
+      <c r="I496" s="2" t="inlineStr">
         <is>
           <t>Roxana Portugal; Juliana Delle Ville; Leandro Antonelli</t>
         </is>
       </c>
-      <c r="J496" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="K496" s="3" t="inlineStr">
-        <is>
-          <t>Roxana L.Q. Portugal → Roxana Portugal [revisar: subset]</t>
-        </is>
-      </c>
-      <c r="L496" s="3" t="n">
+      <c r="J496" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K496" s="2" t="inlineStr">
+        <is>
+          <t>Roxana L.Q. Portugal → Roxana Portugal [manual]</t>
+        </is>
+      </c>
+      <c r="L496" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M496" s="3" t="inlineStr">
+      <c r="M496" s="2" t="inlineStr">
         <is>
           <t>This paper explores the intersection between software development and journalism, highlighting the fundamental importance of implementing non-functional requirements to achieve a balance between immediacy and accuracy. In software development, requirements encompass user needs and demand precise and continuous updates to meet time-to-market demands. In journalism, audience engagement drives the need for precise news coverage, especially with the growth of artificial intelligence (AI). Non-functional requirements (NFRs) have gained relevance, emphasizing the need for effective balance. This work investigates the integration of technologies such as Named Entity Recognition (NER) and topic modeling into news updating processes as means to enhance both efficiency and precision. Additionally, this strategy, beneficial in requirements management and applicable across domains, is explored. The article is structured to delve into the imperatives of news writing, the proposed strategy, potential applications, and directions for future research.</t>
         </is>
       </c>
-      <c r="N496" s="3" t="inlineStr">
+      <c r="N496" s="2" t="inlineStr">
         <is>
           <t>Requirements engineering; Artificial Intelligence (AI); Natural Language Processing (NLP); Journalism; Non-Functional Requirements (NFRs)</t>
         </is>
       </c>
-      <c r="O496" s="3" t="inlineStr">
+      <c r="O496" s="2" t="inlineStr">
         <is>
           <t>10.29327/1407529.27-30</t>
         </is>
       </c>
-      <c r="P496" s="3" t="inlineStr">
+      <c r="P496" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER2024/WER2024_paper_58.pdf</t>
         </is>
       </c>
-      <c r="Q496" s="3" t="inlineStr">
+      <c r="Q496" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER2024/wer202425.html</t>
         </is>
       </c>
-      <c r="R496" s="3" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S496" s="3" t="inlineStr">
+      <c r="R496" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S496" s="2" t="inlineStr">
         <is>
           <t>978-65-01-06131-3</t>
         </is>
       </c>
-      <c r="T496" s="3" t="inlineStr">
+      <c r="T496" s="2" t="inlineStr">
         <is>
           <t>Even3, Brazil</t>
         </is>
       </c>
-      <c r="U496" s="3" t="b">
+      <c r="U496" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -48971,40 +49025,40 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504" s="3" t="inlineStr">
+      <c r="A504" s="2" t="inlineStr">
         <is>
           <t>wer202500</t>
         </is>
       </c>
-      <c r="B504" s="3" t="n">
+      <c r="B504" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="C504" s="3" t="inlineStr">
+      <c r="C504" s="2" t="inlineStr">
         <is>
           <t>WER2025</t>
         </is>
       </c>
-      <c r="D504" s="3" t="inlineStr">
+      <c r="D504" s="2" t="inlineStr">
         <is>
           <t>28th Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E504" s="3" t="inlineStr">
+      <c r="E504" s="2" t="inlineStr">
         <is>
           <t>Rio de Janeiro, Brazil, 20-22 August 2025</t>
         </is>
       </c>
-      <c r="F504" s="3" t="inlineStr">
+      <c r="F504" s="2" t="inlineStr">
         <is>
           <t>Preface</t>
         </is>
       </c>
-      <c r="G504" s="3" t="inlineStr">
+      <c r="G504" s="2" t="inlineStr">
         <is>
           <t>Preface: Proceedings of the 28th Workshop on Requirements Engineering (WER2025)</t>
         </is>
       </c>
-      <c r="H504" s="3" t="inlineStr">
+      <c r="H504" s="2" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Marcela Ridao; </t>
@@ -49017,76 +49071,69 @@
             <t>Márcia Lucena</t>
           </r>
           <r>
-            <t xml:space="preserve">; </t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="00C00000"/>
-            </rPr>
-            <t>Rodrigo Santos</t>
-          </r>
-        </is>
-      </c>
-      <c r="I504" s="3" t="inlineStr">
+            <t>; Rodrigo Santos</t>
+          </r>
+        </is>
+      </c>
+      <c r="I504" s="2" t="inlineStr">
         <is>
           <t>Marcela Ridao; Marcia Lucena; Rodrigo Santos</t>
         </is>
       </c>
-      <c r="J504" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="K504" s="3" t="inlineStr">
-        <is>
-          <t>Márcia Lucena → Marcia Lucena [same_key]; Rodrigo Santos [revisar: ambiguous]</t>
-        </is>
-      </c>
-      <c r="L504" s="3" t="n">
+      <c r="J504" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K504" s="2" t="inlineStr">
+        <is>
+          <t>Márcia Lucena → Marcia Lucena [same_key]; Rodrigo Santos → Rodrigo Santos [manual]</t>
+        </is>
+      </c>
+      <c r="L504" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M504" s="3" t="inlineStr">
+      <c r="M504" s="2" t="inlineStr">
         <is>
           <t>The twenty-eighth edition of the Workshop on Requirements Engineering (WER 2025), hosted at Federal University of Rio de Janeiro State in Rio de Janeiro, Brazil, from August 20th to 22th, 2025, brought together researchers and practitioners from across academia and industry. Over three vibrant days, discussions spanned key themes such as usability, transparency, data protection, natural language processing, sustainability, accessibility, technical debt, and security requirements. This year, 28 articles were presented as full papers. Following a thorough review by at least three committee members per submission. The event featured five tracks: Research, Industry, Master's and Doctoral, Software Requirements Tools, Tutorials. Distinguished keynote speakers included Marcos Kalinowski from PUC-Rio, offering unique insights into cutting-edge challenges in Requirements Engineering.</t>
         </is>
       </c>
-      <c r="N504" s="3" t="inlineStr">
+      <c r="N504" s="2" t="inlineStr">
         <is>
           <t>WER; Requirements Engineering</t>
         </is>
       </c>
-      <c r="O504" s="3" t="inlineStr">
+      <c r="O504" s="2" t="inlineStr">
         <is>
           <t>10.29327/1588952.28-1</t>
         </is>
       </c>
-      <c r="P504" s="3" t="inlineStr">
+      <c r="P504" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER2025/wer202500.pdf</t>
         </is>
       </c>
-      <c r="Q504" s="3" t="inlineStr">
+      <c r="Q504" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER2025/wer202500.html</t>
         </is>
       </c>
-      <c r="R504" s="3" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S504" s="3" t="inlineStr">
+      <c r="R504" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S504" s="2" t="inlineStr">
         <is>
           <t>978-65-01-52831-1</t>
         </is>
       </c>
-      <c r="T504" s="3" t="inlineStr">
+      <c r="T504" s="2" t="inlineStr">
         <is>
           <t>Even3, Brazil</t>
         </is>
       </c>
-      <c r="U504" s="3" t="b">
+      <c r="U504" s="2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -53048,40 +53095,40 @@
       </c>
     </row>
     <row r="543">
-      <c r="A543" s="3" t="inlineStr">
+      <c r="A543" s="2" t="inlineStr">
         <is>
           <t>wer202610</t>
         </is>
       </c>
-      <c r="B543" s="3" t="n">
+      <c r="B543" s="2" t="n">
         <v>2026</v>
       </c>
-      <c r="C543" s="3" t="inlineStr">
+      <c r="C543" s="2" t="inlineStr">
         <is>
           <t>WER2026</t>
         </is>
       </c>
-      <c r="D543" s="3" t="inlineStr">
+      <c r="D543" s="2" t="inlineStr">
         <is>
           <t>29th Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E543" s="3" t="inlineStr">
+      <c r="E543" s="2" t="inlineStr">
         <is>
           <t>La Plata, Argentina, 11-13 August 2026</t>
         </is>
       </c>
-      <c r="F543" s="3" t="inlineStr">
+      <c r="F543" s="2" t="inlineStr">
         <is>
           <t>Research Track</t>
         </is>
       </c>
-      <c r="G543" s="3" t="inlineStr">
+      <c r="G543" s="2" t="inlineStr">
         <is>
           <t>Uso de Abordagens da Engenharia de Requisitos Orientada a Objetivos na Indústria: Uma Revisão Sistemática da Literatura</t>
         </is>
       </c>
-      <c r="H543" s="3" t="inlineStr">
+      <c r="H543" s="2" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Rafael Lima; </t>
@@ -53089,71 +53136,71 @@
           <r>
             <rPr>
               <b val="1"/>
-              <color rgb="00C00000"/>
+              <color rgb="009C5700"/>
             </rPr>
             <t>Victor Santander</t>
           </r>
         </is>
       </c>
-      <c r="I543" s="3" t="inlineStr">
+      <c r="I543" s="2" t="inlineStr">
         <is>
           <t>Rafael Lima; Victor Francisco Araya Santander</t>
         </is>
       </c>
-      <c r="J543" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="K543" s="3" t="inlineStr">
-        <is>
-          <t>Victor Santander → Victor Francisco Araya Santander [revisar: subset]</t>
-        </is>
-      </c>
-      <c r="L543" s="3" t="n">
+      <c r="J543" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K543" s="2" t="inlineStr">
+        <is>
+          <t>Victor Santander → Victor Francisco Araya Santander [manual]</t>
+        </is>
+      </c>
+      <c r="L543" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M543" s="3" t="inlineStr">
+      <c r="M543" s="2" t="inlineStr">
         <is>
           <t>Este artigo apresenta uma Revisão Sistemática da Literatura (RSL) cujo objetivo é identificar e analisar evidências sobre o uso de técnicas e métodos da Engenharia de Requisitos Orientada a Objetivos (GORE) no desenvolvimento de software, com atenção particular ao contexto de pequenas e médias empresas (PMEs). O trabalho foi conduzido seguindo diretrizes consolidadas para RSL na Engenharia de Software. A análise dos estudos selecionados permitiu identificar as principais técnicas da GORE empregadas, as atividades da Engenharia de Requisitos em que são aplicadas e os contextos organizacionais em que têm sido utilizadas, bem como as vantagens e limitações relatadas na literatura. Os resultados indicam que a GORE tem sido amplamente investigada e aplicada em diferentes contextos organizacionais, incluindo PMEs. Observa-se o uso recorrente de técnicas como i*, NFR Framework e KAOS, principalmente nas atividades de elicitação, análise e negociação de requisitos. Entre as principais vantagens relatadas destacam-se a melhoria da comunicação, o alinhamento entre objetivos organizacionais e requisitos de software e o apoio à tomada de decisão. Por outro lado, limitações como a complexidade das técnicas, a curva de aprendizado e o esforço necessário para manutenção dos modelos podem dificultar sua adoção contínua em ambientes industriais.</t>
         </is>
       </c>
-      <c r="N543" s="3" t="inlineStr">
+      <c r="N543" s="2" t="inlineStr">
         <is>
           <t>Engenharia de requisitos orientada a objetivos (GORE); Revisão sistemática da literatura; Pequenas e médias empresas</t>
         </is>
       </c>
-      <c r="O543" s="3" t="inlineStr">
+      <c r="O543" s="2" t="inlineStr">
         <is>
           <t>10.29327/1884517.29-11</t>
         </is>
       </c>
-      <c r="P543" s="3" t="inlineStr">
+      <c r="P543" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER2026/wer202610.pdf</t>
         </is>
       </c>
-      <c r="Q543" s="3" t="inlineStr">
+      <c r="Q543" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER2026/wer202610.html</t>
         </is>
       </c>
-      <c r="R543" s="3" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S543" s="3" t="inlineStr">
+      <c r="R543" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S543" s="2" t="inlineStr">
         <is>
           <t>978-65-02-19591-8</t>
         </is>
       </c>
-      <c r="T543" s="3" t="inlineStr">
+      <c r="T543" s="2" t="inlineStr">
         <is>
           <t>Even3, Brazil</t>
         </is>
       </c>
-      <c r="U543" s="3" t="b">
+      <c r="U543" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -53983,40 +54030,40 @@
       </c>
     </row>
     <row r="552">
-      <c r="A552" s="3" t="inlineStr">
+      <c r="A552" s="2" t="inlineStr">
         <is>
           <t>wer202619</t>
         </is>
       </c>
-      <c r="B552" s="3" t="n">
+      <c r="B552" s="2" t="n">
         <v>2026</v>
       </c>
-      <c r="C552" s="3" t="inlineStr">
+      <c r="C552" s="2" t="inlineStr">
         <is>
           <t>WER2026</t>
         </is>
       </c>
-      <c r="D552" s="3" t="inlineStr">
+      <c r="D552" s="2" t="inlineStr">
         <is>
           <t>29th Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E552" s="3" t="inlineStr">
+      <c r="E552" s="2" t="inlineStr">
         <is>
           <t>La Plata, Argentina, 11-13 August 2026</t>
         </is>
       </c>
-      <c r="F552" s="3" t="inlineStr">
+      <c r="F552" s="2" t="inlineStr">
         <is>
           <t>Research Track</t>
         </is>
       </c>
-      <c r="G552" s="3" t="inlineStr">
+      <c r="G552" s="2" t="inlineStr">
         <is>
           <t>Utilizando a Engenharia de Software Experimental para avaliar a implementação das Regras de Garantia de Consistência na ferramenta JGOOSE</t>
         </is>
       </c>
-      <c r="H552" s="3" t="inlineStr">
+      <c r="H552" s="2" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Kauan Campos; Rafael Lima; </t>
@@ -54024,71 +54071,71 @@
           <r>
             <rPr>
               <b val="1"/>
-              <color rgb="00C00000"/>
+              <color rgb="009C5700"/>
             </rPr>
             <t>Victor Santander</t>
           </r>
         </is>
       </c>
-      <c r="I552" s="3" t="inlineStr">
+      <c r="I552" s="2" t="inlineStr">
         <is>
           <t>Kauan Campos; Rafael Lima; Victor Francisco Araya Santander</t>
         </is>
       </c>
-      <c r="J552" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="K552" s="3" t="inlineStr">
-        <is>
-          <t>Victor Santander → Victor Francisco Araya Santander [revisar: subset]</t>
-        </is>
-      </c>
-      <c r="L552" s="3" t="n">
+      <c r="J552" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K552" s="2" t="inlineStr">
+        <is>
+          <t>Victor Santander → Victor Francisco Araya Santander [manual]</t>
+        </is>
+      </c>
+      <c r="L552" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M552" s="3" t="inlineStr">
+      <c r="M552" s="2" t="inlineStr">
         <is>
           <t>A Engenharia de Requisitos de Software busca identificar, documentar e gerenciar requisitos ao longo do ciclo de vida de sistemas, sendo a consistência entre diferentes modelos um desafio recorrente na Engenharia de Software. Modelos como iStar e Casos de Uso da UML são amplamente utilizados, mas sua integração exige mecanismos que assegurem coerência entre artefatos ao longo da evolução do software. Este estudo tem como objetivo avaliar a implementação das Regras de Garantia de Consistência na ferramenta JGOOSE, verificando sua capacidade de manter a consistência semiautomática entre casos de uso e modelos iStar. A pesquisa foi conduzida sob princípios da Engenharia de Software Experimental, utilizando a estratégia de quase-experimento. O planejamento envolveu hipóteses formais, definição de variáveis e aplicação da abordagem GQM para estruturar métricas de avaliação. Os resultados indicam que, mesmo havendo oportunidades para ajustes futuros, as Regras de Garantia de Consistência foram aplicadas corretamente em diversos cenários, garantindo a derivação semi-automática consistente entre os modelos e contribuindo para a evolução da ferramenta.</t>
         </is>
       </c>
-      <c r="N552" s="3" t="inlineStr">
+      <c r="N552" s="2" t="inlineStr">
         <is>
           <t>Engenharia de software experimental; Derivação semi-automática; Ferramenta CASE</t>
         </is>
       </c>
-      <c r="O552" s="3" t="inlineStr">
+      <c r="O552" s="2" t="inlineStr">
         <is>
           <t>10.29327/1884517.29-20</t>
         </is>
       </c>
-      <c r="P552" s="3" t="inlineStr">
+      <c r="P552" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER2026/wer202619.pdf</t>
         </is>
       </c>
-      <c r="Q552" s="3" t="inlineStr">
+      <c r="Q552" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER2026/wer202619.html</t>
         </is>
       </c>
-      <c r="R552" s="3" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S552" s="3" t="inlineStr">
+      <c r="R552" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S552" s="2" t="inlineStr">
         <is>
           <t>978-65-02-19591-8</t>
         </is>
       </c>
-      <c r="T552" s="3" t="inlineStr">
+      <c r="T552" s="2" t="inlineStr">
         <is>
           <t>Even3, Brazil</t>
         </is>
       </c>
-      <c r="U552" s="3" t="b">
+      <c r="U552" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -54591,40 +54638,40 @@
       </c>
     </row>
     <row r="558">
-      <c r="A558" s="3" t="inlineStr">
+      <c r="A558" s="2" t="inlineStr">
         <is>
           <t>wer202625</t>
         </is>
       </c>
-      <c r="B558" s="3" t="n">
+      <c r="B558" s="2" t="n">
         <v>2026</v>
       </c>
-      <c r="C558" s="3" t="inlineStr">
+      <c r="C558" s="2" t="inlineStr">
         <is>
           <t>WER2026</t>
         </is>
       </c>
-      <c r="D558" s="3" t="inlineStr">
+      <c r="D558" s="2" t="inlineStr">
         <is>
           <t>29th Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E558" s="3" t="inlineStr">
+      <c r="E558" s="2" t="inlineStr">
         <is>
           <t>La Plata, Argentina, 11-13 August 2026</t>
         </is>
       </c>
-      <c r="F558" s="3" t="inlineStr">
+      <c r="F558" s="2" t="inlineStr">
         <is>
           <t>Masters and Doctoral Track</t>
         </is>
       </c>
-      <c r="G558" s="3" t="inlineStr">
+      <c r="G558" s="2" t="inlineStr">
         <is>
           <t>Uma Abordagem para Elicitação de Requisitos em Ambientes Ágeis baseada na Integração entre Design Thinking e Engenharia de Requisitos</t>
         </is>
       </c>
-      <c r="H558" s="3" t="inlineStr">
+      <c r="H558" s="2" t="inlineStr">
         <is>
           <r>
             <t>Maria Augusta Nascimento de Moura;</t>
@@ -54632,71 +54679,71 @@
           <r>
             <rPr>
               <b val="1"/>
-              <color rgb="00C00000"/>
+              <color rgb="009C5700"/>
             </rPr>
             <t>Fernanda Maria Ribeiro de Alencar</t>
           </r>
         </is>
       </c>
-      <c r="I558" s="3" t="inlineStr">
+      <c r="I558" s="2" t="inlineStr">
         <is>
           <t>Maria Augusta Nascimento de Moura; Fernanda Alencar</t>
         </is>
       </c>
-      <c r="J558" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="K558" s="3" t="inlineStr">
-        <is>
-          <t>Fernanda Maria Ribeiro de Alencar → Fernanda Alencar [revisar: subset]</t>
-        </is>
-      </c>
-      <c r="L558" s="3" t="n">
+      <c r="J558" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K558" s="2" t="inlineStr">
+        <is>
+          <t>Fernanda Maria Ribeiro de Alencar → Fernanda Alencar [manual]</t>
+        </is>
+      </c>
+      <c r="L558" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M558" s="3" t="inlineStr">
+      <c r="M558" s="2" t="inlineStr">
         <is>
           <t>No contexto do desenvolvimento de software, a Engenharia de Requisitos desempenha papel fundamental na compreensão e definição das necessidades dos stakeholders. Em ambientes ágeis, no entanto, essa atividade enfrenta desafios relacionados à compreensão do problema, à comunicação entre os envolvidos e à adaptação a mudanças, o que pode impactar diretamente a qualidade dos requisitos definidos. Como alter- nativa, o Design Thinking tem sido explorado como uma abordagem complementar, por promover uma perspectiva centrada no usuário e fa- vorecer a exploração do problema antes da definição da solução. Diante desse cenário, este trabalho tem como objetivo propor um guia prático que apoie a elicitação de requisitos por meio da integração entre Design Thinking e Engenharia de Requisitos em ambientes ágeis. Para isso, será conduzida uma Revisão Rápida da Literatura, com o intuito de iden- tificar práticas, contribuições e lacunas relacionadas a essa integração. Como resultado, espera-se contribuir para a definição de requisitos mais claros, consistentes e alinhados às necessidades dos stakeholders.</t>
         </is>
       </c>
-      <c r="N558" s="3" t="inlineStr">
+      <c r="N558" s="2" t="inlineStr">
         <is>
           <t>Engenharia de Requisitos; Design Thinking; Métodos Ágeis; Elicitação de Requisitos</t>
         </is>
       </c>
-      <c r="O558" s="3" t="inlineStr">
+      <c r="O558" s="2" t="inlineStr">
         <is>
           <t>10.29327/1884517.29-26</t>
         </is>
       </c>
-      <c r="P558" s="3" t="inlineStr">
+      <c r="P558" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER2026/wer202625.pdf</t>
         </is>
       </c>
-      <c r="Q558" s="3" t="inlineStr">
+      <c r="Q558" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER2026/wer202625.html</t>
         </is>
       </c>
-      <c r="R558" s="3" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S558" s="3" t="inlineStr">
+      <c r="R558" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S558" s="2" t="inlineStr">
         <is>
           <t>978-65-02-19591-8</t>
         </is>
       </c>
-      <c r="T558" s="3" t="inlineStr">
+      <c r="T558" s="2" t="inlineStr">
         <is>
           <t>Even3, Brazil</t>
         </is>
       </c>
-      <c r="U558" s="3" t="b">
+      <c r="U558" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -55035,40 +55082,40 @@
       </c>
     </row>
     <row r="562">
-      <c r="A562" s="3" t="inlineStr">
+      <c r="A562" s="2" t="inlineStr">
         <is>
           <t>wer202629</t>
         </is>
       </c>
-      <c r="B562" s="3" t="n">
+      <c r="B562" s="2" t="n">
         <v>2026</v>
       </c>
-      <c r="C562" s="3" t="inlineStr">
+      <c r="C562" s="2" t="inlineStr">
         <is>
           <t>WER2026</t>
         </is>
       </c>
-      <c r="D562" s="3" t="inlineStr">
+      <c r="D562" s="2" t="inlineStr">
         <is>
           <t>29th Workshop on Requirements Engineering</t>
         </is>
       </c>
-      <c r="E562" s="3" t="inlineStr">
+      <c r="E562" s="2" t="inlineStr">
         <is>
           <t>La Plata, Argentina, 11-13 August 2026</t>
         </is>
       </c>
-      <c r="F562" s="3" t="inlineStr">
+      <c r="F562" s="2" t="inlineStr">
         <is>
           <t>Industry Track</t>
         </is>
       </c>
-      <c r="G562" s="3" t="inlineStr">
+      <c r="G562" s="2" t="inlineStr">
         <is>
           <t>From Workshop Transcripts to Requirements Models - A Heuristic and RAG-Based Approach for Reusing Elicitation Data</t>
         </is>
       </c>
-      <c r="H562" s="3" t="inlineStr">
+      <c r="H562" s="2" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Roxana Portugal; </t>
@@ -55096,71 +55143,71 @@
           <r>
             <rPr>
               <b val="1"/>
-              <color rgb="00C00000"/>
+              <color rgb="009C5700"/>
             </rPr>
             <t>Edgar Sarmiento</t>
           </r>
         </is>
       </c>
-      <c r="I562" s="3" t="inlineStr">
+      <c r="I562" s="2" t="inlineStr">
         <is>
           <t>Roxana Portugal; Julio Cesar Sampaio do Prado Leite; Lyrene Fernandes da Silva; Edgar Sarmiento Calisaya</t>
         </is>
       </c>
-      <c r="J562" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="K562" s="3" t="inlineStr">
-        <is>
-          <t>Julio C. S. P. Leite → Julio Cesar Sampaio do Prado Leite [subset]; Lyrene F. Silva → Lyrene Fernandes da Silva [subset]; Edgar Sarmiento → Edgar Sarmiento Calisaya [revisar: surname_not_last]</t>
-        </is>
-      </c>
-      <c r="L562" s="3" t="n">
+      <c r="J562" s="2" t="inlineStr">
+        <is>
+          <t>ajustado</t>
+        </is>
+      </c>
+      <c r="K562" s="2" t="inlineStr">
+        <is>
+          <t>Julio C. S. P. Leite → Julio Cesar Sampaio do Prado Leite [subset]; Lyrene F. Silva → Lyrene Fernandes da Silva [subset]; Edgar Sarmiento → Edgar Sarmiento Calisaya [manual]</t>
+        </is>
+      </c>
+      <c r="L562" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="M562" s="3" t="inlineStr">
+      <c r="M562" s="2" t="inlineStr">
         <is>
           <t>Elicitation activities such as workshops generate rich qualitative data; however their reuse in Requirements Engineering (RE) remains limited due to the lack of explicit structure and traceable interpretation. While modeling approaches such as i* and the NFR Framework define modeling constructs, they do not make explicit how model elements are derived from elicitation data.  In this paper, we present an industrial case based on workshop transcripts and conduct an exploratory exercise of how RE engineers derive goals, tasks, and quality concerns from the same textual input. From a limited but representative sample, we identify recurring patterns in their interpretive reasoning and derive an initial set of heuristics that make this reasoning explicit. We further illustrate how these heuristics can be operationalized within a Retrieval-Augmented Generation (RAG) pipeline, enabling semantic and semi-automated processing grounded in RE engineers’ interpretations while preserving traceability. Our results suggest that, in this exploratory setting, making interpretative reasoning explicit supports the reuse of elicitation data through requirements models.</t>
         </is>
       </c>
-      <c r="N562" s="3" t="inlineStr">
+      <c r="N562" s="2" t="inlineStr">
         <is>
           <t>Elicitation Data; Requirements Modeling; Interpretative Reasoning; Data Reuse; Qualitative Data; Semantic Analysis.</t>
         </is>
       </c>
-      <c r="O562" s="3" t="inlineStr">
+      <c r="O562" s="2" t="inlineStr">
         <is>
           <t>10.29327/1884517.29-30</t>
         </is>
       </c>
-      <c r="P562" s="3" t="inlineStr">
+      <c r="P562" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/papers/WER2026/wer202629.pdf</t>
         </is>
       </c>
-      <c r="Q562" s="3" t="inlineStr">
+      <c r="Q562" s="2" t="inlineStr">
         <is>
           <t>https://werpapers.dimap.ufrn.br/proceedings/WER2026/wer202629.html</t>
         </is>
       </c>
-      <c r="R562" s="3" t="inlineStr">
-        <is>
-          <t>2675-0066</t>
-        </is>
-      </c>
-      <c r="S562" s="3" t="inlineStr">
+      <c r="R562" s="2" t="inlineStr">
+        <is>
+          <t>2675-0066</t>
+        </is>
+      </c>
+      <c r="S562" s="2" t="inlineStr">
         <is>
           <t>978-65-02-19591-8</t>
         </is>
       </c>
-      <c r="T562" s="3" t="inlineStr">
+      <c r="T562" s="2" t="inlineStr">
         <is>
           <t>Even3, Brazil</t>
         </is>
       </c>
-      <c r="U562" s="3" t="b">
+      <c r="U562" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -55273,7 +55320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -55313,698 +55360,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alexandre M. L. de Vasconcelos</t>
+          <t>Rodrigo Santos</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Alexandre Marcos Lins de Vasconcelos</t>
+          <t>Rodrigo Santos</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>subset</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
+          <t>ambiguous</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>wer201213</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Ariadne Carvalho</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Ariadne M. B. R. Carvalho</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>subset</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>wer200602</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Carlos Lahoz</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Carlos Henrique Netto Lahoz</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>subset</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>wer200603</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>D. Bolchini</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Davide Bolchini</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>initials</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>wer200206</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Edgar Sarmiento</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Edgar Sarmiento Calisaya</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>surname_not_last</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>wer202629</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Enyo José Tavares Gonçalves</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Enyo Gonçalves</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>subset</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>wer202202</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Eric S.K. Yu</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Eric Yu</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>subset</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>wer200706</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Fernanda Maria Ribeiro de Alencar</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Fernanda Alencar</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>subset</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>wer202625</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>F.A.C. Pinheiro</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Francisco A. C. Pinheiro</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>initials</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>wer200216</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Johnny Marques</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Johnny Cardoso Marques</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>subset</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>wer202127</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Jorge Luis Nicolas Audy</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Jorge Luis N. Audy</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>subset</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>wer200914</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Juan Sánchez Diaz</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Juan Sánchez</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>surname_not_last</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>wer200112</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>J. Sánchez</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Juan Sánchez</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>surname_not_last</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>wer200219</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Leandro Lopes</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Leandro T. Lopes</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>subset</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>wer200513</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Luciana C. Ballejos</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Luciana Ballejos</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>subset</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>wer200409</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>L.E.G. Martins</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Luiz Eduardo Galvão Martins</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>initials</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>wer200213</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>M. Toranzo</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Marco A. Toranzo Céspedes</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>surname_not_last</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>wer200209</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>M.A. Laguna</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Miguel A. Laguna</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>initials</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>wer200220</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>O. Ormandjieva</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Olga Ormandjieva</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>initials</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>wer200719</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Paulo C. Masiero</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Paulo Cesar Masiero</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>subset</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>wer199811</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Renato de Freitas Bulcão Neto</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Renato F. Bulcão-Neto</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>subset</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>wer201604</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>R. de A. Falbo</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Ricardo de Almeida Falbo</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>initials</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>wer200212</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Roberta Fagundes</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Roberta Andrade de A. Fagundes</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>subset</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>wer201815</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Rodrigo Santos</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Rodrigo Santos</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>ambiguous</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
           <t>wer201005, wer202306, wer202500</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Roxana L.Q. Portugal</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Roxana Portugal</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>subset</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>wer202300, wer202425</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Tereza G. Kirner</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Tereza Gonçalves Kirner</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>subset</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>wer200615</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Victor Santander</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Victor Francisco Araya Santander</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>subset</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>wer202125, wer202200, wer202610, wer202619</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Wylliams Santos</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Wylliams Barbosa Santos</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>subset</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>wer201816</t>
         </is>
       </c>
     </row>
@@ -56027,84 +55399,84 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Situação dos nomes (coluna name_status)</t>
         </is>
       </c>
-      <c r="B1" s="5" t="n"/>
+      <c r="B1" s="4" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>revisar</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Linha em vermelho claro. Há nome cuja normalização é incerta: sem coautor em comum com as demais variantes, união por iniciais, sobrenome que não é o último, ou variante ambígua. O nome aparece em vermelho e negrito na coluna authors.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>ajustado</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Linha em amarelo. Algum nome foi normalizado ou a separação dos autores foi corrigida. O nome aparece em laranja e negrito na coluna authors.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Sem alteração.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n"/>
-      <c r="B5" s="5" t="n"/>
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>name_changes</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Lista 'original → canônico [regra]' dos nomes alterados no artigo.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>revisar_nomes</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Aba com cada nome a revisar e os artigos em que aparece.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Como corrigir</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Adicionar linha em data/author_overrides.csv (variant,canonical) e rodar normalize_authors.py. canonical vazio impede a união.</t>
         </is>
